--- a/nino/ROTICERIA/Estructura_Costos_Rotiseria_NINO.xlsx
+++ b/nino/ROTICERIA/Estructura_Costos_Rotiseria_NINO.xlsx
@@ -20,7 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="9">
     <font>
       <name val="Calibri"/>
@@ -142,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -165,24 +167,51 @@
     <xf numFmtId="3" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -639,8 +668,9 @@
           <t>VENTAS BRUTAS (con IVA)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>13370919</v>
+      <c r="B6" s="6">
+        <f>B8*1.21</f>
+        <v/>
       </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr">
@@ -660,8 +690,9 @@
           <t>(-) IVA Debito Fiscal</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>-2320573</v>
+      <c r="B7" s="6">
+        <f>-B8*0.21</f>
+        <v/>
       </c>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="5" t="inlineStr">
@@ -710,7 +741,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Efectivo 40.8% | Debito 26.7% | Credito 19.0% | Billetera 10.1%</t>
+          <t xml:space="preserve">  Efectivo 40.8% | Debito 26.7% | Credito 19.0% | Billetera 13.4%</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr"/>
@@ -758,13 +789,13 @@
           <t>COSTO TOTAL INSUMOS</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
-        <v>-7735242</v>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>70.0%</t>
-        </is>
+      <c r="B14" s="11">
+        <f>-B8*0.7</f>
+        <v/>
+      </c>
+      <c r="C14" s="12">
+        <f>ABS(B14)/B8</f>
+        <v/>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
@@ -783,7 +814,7 @@
           <t xml:space="preserve">  Empanadas</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="13" t="n">
         <v>-3855659</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -808,7 +839,7 @@
           <t xml:space="preserve">  Carnes elaboradas</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="13" t="n">
         <v>-1709147</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -833,7 +864,7 @@
           <t xml:space="preserve">  Pizzas y canelones</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="13" t="n">
         <v>-660855</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -858,7 +889,7 @@
           <t xml:space="preserve">  Milanesas</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="13" t="n">
         <v>-431885</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -883,7 +914,7 @@
           <t xml:space="preserve">  Salsas</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="13" t="n">
         <v>-163088</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -908,7 +939,7 @@
           <t xml:space="preserve">  Otros elaborados</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="13" t="n">
         <v>-914608</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -933,18 +964,19 @@
           <t>MARGEN BRUTO</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
-        <v>3315104</v>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
+      <c r="B21" s="8">
+        <f>B8+B14</f>
+        <v/>
+      </c>
+      <c r="C21" s="14">
+        <f>B21/B8</f>
+        <v/>
       </c>
       <c r="D21" s="7" t="inlineStr"/>
-      <c r="E21" s="7">
-        <f> Ventas - CMV</f>
-        <v/>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Ventas - CMV</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -989,15 +1021,15 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>3.1 SUELDOS Y CARGAS SOCIALES</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr"/>
-      <c r="C26" s="13" t="inlineStr"/>
-      <c r="D26" s="13" t="inlineStr"/>
-      <c r="E26" s="13" t="inlineStr"/>
+      <c r="B26" s="15" t="inlineStr"/>
+      <c r="C26" s="15" t="inlineStr"/>
+      <c r="D26" s="15" t="inlineStr"/>
+      <c r="E26" s="15" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1005,13 +1037,13 @@
           <t>Sueldos brutos (3 empleados)</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n">
-        <v>-3540822</v>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>32.0%</t>
-        </is>
+      <c r="B27" s="6">
+        <f>B28+B29</f>
+        <v/>
+      </c>
+      <c r="C27" s="16">
+        <f>ABS(B27)/B8</f>
+        <v/>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
@@ -1030,7 +1062,7 @@
           <t xml:space="preserve">  - Remunerativo</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="13" t="n">
         <v>-3240822</v>
       </c>
       <c r="C28" s="9" t="inlineStr"/>
@@ -1051,7 +1083,7 @@
           <t xml:space="preserve">  - No Remunerativo</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="13" t="n">
         <v>-300000</v>
       </c>
       <c r="C29" s="9" t="inlineStr"/>
@@ -1072,13 +1104,13 @@
           <t>Contribuciones patronales (F.930)</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n">
-        <v>-963820</v>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>8.7%</t>
-        </is>
+      <c r="B30" s="6">
+        <f>B28*0.2974</f>
+        <v/>
+      </c>
+      <c r="C30" s="16">
+        <f>ABS(B30)/B8</f>
+        <v/>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
@@ -1097,8 +1129,9 @@
           <t xml:space="preserve">  - Jubilacion (SIPA)</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n">
-        <v>-411908</v>
+      <c r="B31" s="13">
+        <f>B28*0.1271</f>
+        <v/>
       </c>
       <c r="C31" s="9" t="inlineStr"/>
       <c r="D31" s="9" t="inlineStr">
@@ -1118,8 +1151,9 @@
           <t xml:space="preserve">  - PAMI (Ley 19.032)</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n">
-        <v>-51205</v>
+      <c r="B32" s="13">
+        <f>B28*0.0158</f>
+        <v/>
       </c>
       <c r="C32" s="9" t="inlineStr"/>
       <c r="D32" s="9" t="inlineStr">
@@ -1135,8 +1169,9 @@
           <t xml:space="preserve">  - Asignaciones Familiares</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
-        <v>-180190</v>
+      <c r="B33" s="13">
+        <f>B28*0.0556</f>
+        <v/>
       </c>
       <c r="C33" s="9" t="inlineStr"/>
       <c r="D33" s="9" t="inlineStr">
@@ -1152,8 +1187,9 @@
           <t xml:space="preserve">  - Fondo Nacional de Empleo</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n">
-        <v>-28843</v>
+      <c r="B34" s="13">
+        <f>B28*0.0089</f>
+        <v/>
       </c>
       <c r="C34" s="9" t="inlineStr"/>
       <c r="D34" s="9" t="inlineStr">
@@ -1169,8 +1205,9 @@
           <t xml:space="preserve">  - Obra Social patronal</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n">
-        <v>-194449</v>
+      <c r="B35" s="13">
+        <f>B28*0.06</f>
+        <v/>
       </c>
       <c r="C35" s="9" t="inlineStr"/>
       <c r="D35" s="9" t="inlineStr">
@@ -1186,8 +1223,9 @@
           <t xml:space="preserve">  - ART (estimado)</t>
         </is>
       </c>
-      <c r="B36" s="12" t="n">
-        <v>-97225</v>
+      <c r="B36" s="13">
+        <f>B28*0.03</f>
+        <v/>
       </c>
       <c r="C36" s="9" t="inlineStr"/>
       <c r="D36" s="9" t="inlineStr">
@@ -1207,13 +1245,13 @@
           <t>SAC proporcional (1/12)</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n">
-        <v>-350387</v>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
+      <c r="B37" s="6">
+        <f>(B28+B30)/12</f>
+        <v/>
+      </c>
+      <c r="C37" s="16">
+        <f>ABS(B37)/B8</f>
+        <v/>
       </c>
       <c r="D37" s="5" t="inlineStr"/>
       <c r="E37" s="5" t="inlineStr">
@@ -1228,7 +1266,7 @@
           <t>Seguro Vida Obligatorio</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n">
+      <c r="B38" s="13" t="n">
         <v>-1500</v>
       </c>
       <c r="C38" s="9" t="inlineStr"/>
@@ -1244,32 +1282,32 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>SUBTOTAL LABORAL</t>
         </is>
       </c>
-      <c r="B39" s="15" t="n">
-        <v>-4856529</v>
-      </c>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>43.9%</t>
-        </is>
-      </c>
-      <c r="D39" s="14" t="inlineStr"/>
-      <c r="E39" s="14" t="inlineStr"/>
+      <c r="B39" s="18">
+        <f>B27+B30+B37+B38</f>
+        <v/>
+      </c>
+      <c r="C39" s="19">
+        <f>ABS(B39)/B8</f>
+        <v/>
+      </c>
+      <c r="D39" s="17" t="inlineStr"/>
+      <c r="E39" s="17" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>3.2 SERVICIOS (prorrateo rotiseria)</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr"/>
-      <c r="C41" s="13" t="inlineStr"/>
-      <c r="D41" s="13" t="inlineStr"/>
-      <c r="E41" s="13" t="inlineStr"/>
+      <c r="B41" s="15" t="inlineStr"/>
+      <c r="C41" s="15" t="inlineStr"/>
+      <c r="D41" s="15" t="inlineStr"/>
+      <c r="E41" s="15" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -1280,10 +1318,9 @@
       <c r="B42" s="6" t="n">
         <v>-148450</v>
       </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>1.3%</t>
-        </is>
+      <c r="C42" s="16">
+        <f>ABS(B42)/B8</f>
+        <v/>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
@@ -1327,10 +1364,9 @@
       <c r="B45" s="6" t="n">
         <v>-182881</v>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>1.7%</t>
-        </is>
+      <c r="C45" s="16">
+        <f>ABS(B45)/B8</f>
+        <v/>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
@@ -1366,885 +1402,784 @@
       <c r="E47" s="9" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>SUBTOTAL SERVICIOS</t>
         </is>
       </c>
-      <c r="B48" s="15" t="n">
-        <v>-331331</v>
-      </c>
-      <c r="C48" s="14" t="inlineStr">
+      <c r="B48" s="18">
+        <f>B42+B45</f>
+        <v/>
+      </c>
+      <c r="C48" s="19">
+        <f>ABS(B48)/B8</f>
+        <v/>
+      </c>
+      <c r="D48" s="17" t="inlineStr"/>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>Basado en facturas reales Feb-Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>3.3 OTROS COSTOS FIJOS (estimados)</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr"/>
+      <c r="C50" s="15" t="inlineStr"/>
+      <c r="D50" s="15" t="inlineStr"/>
+      <c r="E50" s="15" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Descartables / packaging</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="n">
+        <v>-80000</v>
+      </c>
+      <c r="C51" s="22">
+        <f>ABS(B51)/B8</f>
+        <v/>
+      </c>
+      <c r="D51" s="20" t="inlineStr"/>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>Bandejas aluminio, bolsas, film, envases</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mantenimiento equipos</t>
+        </is>
+      </c>
+      <c r="B52" s="21" t="n">
+        <v>-30000</v>
+      </c>
+      <c r="C52" s="22">
+        <f>ABS(B52)/B8</f>
+        <v/>
+      </c>
+      <c r="D52" s="20" t="inlineStr"/>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>Service horno + heladera, repuestos amort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Indumentaria / EPP</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="C53" s="22">
+        <f>ABS(B53)/B8</f>
+        <v/>
+      </c>
+      <c r="D53" s="20" t="inlineStr"/>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>Delantales, gorros, guantes (3 empleados)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Habilitacion bromatologica</t>
+        </is>
+      </c>
+      <c r="B54" s="21" t="n">
+        <v>-12000</v>
+      </c>
+      <c r="C54" s="22">
+        <f>ABS(B54)/B8</f>
+        <v/>
+      </c>
+      <c r="D54" s="20" t="inlineStr"/>
+      <c r="E54" s="20" t="inlineStr">
+        <is>
+          <t>Anual / 12. Obligatoria elaboracion alimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Habilitacion municipal</t>
+        </is>
+      </c>
+      <c r="B55" s="21" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="C55" s="22">
+        <f>ABS(B55)/B8</f>
+        <v/>
+      </c>
+      <c r="D55" s="20" t="inlineStr"/>
+      <c r="E55" s="20" t="inlineStr">
+        <is>
+          <t>Tasa comercio Lujan de Cuyo / 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>SUBTOTAL OTROS FIJOS</t>
+        </is>
+      </c>
+      <c r="B56" s="18">
+        <f>SUM(B51:B55)</f>
+        <v/>
+      </c>
+      <c r="C56" s="19">
+        <f>ABS(B56)/B8</f>
+        <v/>
+      </c>
+      <c r="D56" s="17" t="inlineStr"/>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>Estimados - ajustar con datos reales</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS FIJOS</t>
+        </is>
+      </c>
+      <c r="B58" s="11">
+        <f>B39+B48+B56</f>
+        <v/>
+      </c>
+      <c r="C58" s="12">
+        <f>ABS(B58)/B8</f>
+        <v/>
+      </c>
+      <c r="D58" s="10" t="inlineStr"/>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>Laboral + Servicios + Otros</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>4. COSTOS VARIABLES (% sobre ventas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Monto Mensual ($)</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>% s/Ventas</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Tasa/Base</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>4.1 COMISIONES TARJETAS</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr"/>
+      <c r="C62" s="15" t="inlineStr"/>
+      <c r="D62" s="15" t="inlineStr"/>
+      <c r="E62" s="15" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Tarjeta Credito (19.0% ventas)</t>
+        </is>
+      </c>
+      <c r="B63" s="6">
+        <f>-B8*0.190142*0.03</f>
+        <v/>
+      </c>
+      <c r="C63" s="23">
+        <f>ABS(B63)/B8</f>
+        <v/>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>3.0%</t>
         </is>
       </c>
-      <c r="D48" s="14" t="inlineStr"/>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t>Basado en facturas reales Feb-Mar 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>3.3 OTROS COSTOS FIJOS (estimados)</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="inlineStr"/>
-      <c r="C50" s="13" t="inlineStr"/>
-      <c r="D50" s="13" t="inlineStr"/>
-      <c r="E50" s="13" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Alquiler / amort. inmueble (prorrateo)</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="n">
-        <v>-150000</v>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="D51" s="16" t="inlineStr"/>
-      <c r="E51" s="16" t="inlineStr">
-        <is>
-          <t>~15% m2 rotiseria s/total local. AJUSTAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Descartables / packaging</t>
-        </is>
-      </c>
-      <c r="B52" s="17" t="n">
-        <v>-80000</v>
-      </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="D52" s="16" t="inlineStr"/>
-      <c r="E52" s="16" t="inlineStr">
-        <is>
-          <t>Bandejas aluminio, bolsas, film, envases</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Amortizacion equipos</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="n">
-        <v>-50000</v>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D53" s="16" t="inlineStr"/>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>Horno, heladera, vitrina. ~$15M equipo / 60 meses</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Mantenimiento equipos</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="n">
-        <v>-30000</v>
-      </c>
-      <c r="C54" s="16" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D54" s="16" t="inlineStr"/>
-      <c r="E54" s="16" t="inlineStr">
-        <is>
-          <t>Service horno y heladeras, repuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Seguros (incendio, RC)</t>
-        </is>
-      </c>
-      <c r="B55" s="17" t="n">
-        <v>-25000</v>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D55" s="16" t="inlineStr"/>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>Prorrateo por m2 rotiseria</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Indumentaria / EPP</t>
-        </is>
-      </c>
-      <c r="B56" s="17" t="n">
-        <v>-15000</v>
-      </c>
-      <c r="C56" s="16" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D56" s="16" t="inlineStr"/>
-      <c r="E56" s="16" t="inlineStr">
-        <is>
-          <t>Delantales, gorros, guantes (3 empleados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Agua (prorrateo)</t>
-        </is>
-      </c>
-      <c r="B57" s="17" t="n">
-        <v>-15000</v>
-      </c>
-      <c r="C57" s="16" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="inlineStr"/>
-      <c r="E57" s="16" t="inlineStr">
-        <is>
-          <t>Limpieza y coccion</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Habilitacion bromatologica</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="n">
-        <v>-12000</v>
-      </c>
-      <c r="C58" s="16" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="inlineStr"/>
-      <c r="E58" s="16" t="inlineStr">
-        <is>
-          <t>Anual / 12. Obligatoria elaboracion alimentos</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Habilitacion municipal</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="n">
-        <v>-8000</v>
-      </c>
-      <c r="C59" s="16" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D59" s="16" t="inlineStr"/>
-      <c r="E59" s="16" t="inlineStr">
-        <is>
-          <t>Tasa comercio Lujan de Cuyo / 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="14" t="inlineStr">
-        <is>
-          <t>SUBTOTAL OTROS FIJOS</t>
-        </is>
-      </c>
-      <c r="B60" s="15" t="n">
-        <v>-385000</v>
-      </c>
-      <c r="C60" s="14" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="D60" s="14" t="inlineStr"/>
-      <c r="E60" s="14" t="inlineStr">
-        <is>
-          <t>Estimados - ajustar con datos reales</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>TOTAL COSTOS FIJOS</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="n">
-        <v>-5572860</v>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>50.4%</t>
-        </is>
-      </c>
-      <c r="D62" s="10" t="inlineStr"/>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>Laboral + Servicios + Otros (estimados)</t>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Naranja 41%, Visa 41%, MC 15%</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>4. COSTOS VARIABLES (% sobre ventas)</t>
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Tarjeta Debito (26.7% ventas)</t>
+        </is>
+      </c>
+      <c r="B64" s="6">
+        <f>-B8*0.267352*0.012</f>
+        <v/>
+      </c>
+      <c r="C64" s="23">
+        <f>ABS(B64)/B8</f>
+        <v/>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Visa 64%, Mastercard 36%</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>Concepto</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Monto Mensual ($)</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>% s/Ventas</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>Tasa/Base</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>Notas</t>
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Billetera Virtual (13.4% ventas)</t>
+        </is>
+      </c>
+      <c r="B65" s="6">
+        <f>-B8*0.134232*0.015</f>
+        <v/>
+      </c>
+      <c r="C65" s="23">
+        <f>ABS(B65)/B8</f>
+        <v/>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Mercado Pago y otras</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="13" t="inlineStr">
-        <is>
-          <t>4.1 COMISIONES TARJETAS</t>
-        </is>
-      </c>
-      <c r="B66" s="13" t="inlineStr"/>
-      <c r="C66" s="13" t="inlineStr"/>
-      <c r="D66" s="13" t="inlineStr"/>
-      <c r="E66" s="13" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>Tarjeta Credito (19.0% ventas)</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="n">
-        <v>-63034</v>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>0.57%</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>Naranja 41%, Visa 41%, MC 15%</t>
-        </is>
-      </c>
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>Subtotal comisiones</t>
+        </is>
+      </c>
+      <c r="B66" s="25">
+        <f>B63+B64+B65</f>
+        <v/>
+      </c>
+      <c r="C66" s="26">
+        <f>ABS(B66)/B8</f>
+        <v/>
+      </c>
+      <c r="D66" s="24" t="inlineStr"/>
+      <c r="E66" s="24" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>Tarjeta Debito (26.7% ventas)</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="n">
-        <v>-35452</v>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>0.32%</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>Visa 64%, Mastercard 36%</t>
-        </is>
-      </c>
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>4.2 IMPUESTOS OPERATIVOS</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr"/>
+      <c r="C68" s="15" t="inlineStr"/>
+      <c r="D68" s="15" t="inlineStr"/>
+      <c r="E68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Billetera Virtual (10.1% ventas)</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="n">
-        <v>-16681</v>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>0.15%</t>
-        </is>
+          <t>Ingresos Brutos (Mendoza)</t>
+        </is>
+      </c>
+      <c r="B69" s="6">
+        <f>-B8*0.03</f>
+        <v/>
+      </c>
+      <c r="C69" s="16">
+        <f>ABS(B69)/B8</f>
+        <v/>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Mercado Pago y otras</t>
+          <t>Ley Impositiva Mza 2026, Rubro 7 comercio minorista</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="18" t="inlineStr">
-        <is>
-          <t>Subtotal comisiones</t>
-        </is>
-      </c>
-      <c r="B70" s="19" t="n">
-        <v>-115167</v>
-      </c>
-      <c r="C70" s="18" t="inlineStr">
-        <is>
-          <t>1.04%</t>
-        </is>
-      </c>
-      <c r="D70" s="18" t="inlineStr"/>
-      <c r="E70" s="18" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="13" t="inlineStr">
-        <is>
-          <t>4.2 IMPUESTOS OPERATIVOS</t>
-        </is>
-      </c>
-      <c r="B72" s="13" t="inlineStr"/>
-      <c r="C72" s="13" t="inlineStr"/>
-      <c r="D72" s="13" t="inlineStr"/>
-      <c r="E72" s="13" t="inlineStr"/>
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Imp. Debitos y Creditos Bancarios</t>
+        </is>
+      </c>
+      <c r="B70" s="6">
+        <f>-B8*0.591727*0.012</f>
+        <v/>
+      </c>
+      <c r="C70" s="23">
+        <f>ABS(B70)/B8</f>
+        <v/>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>1.2% s/banc.</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>Ley 25.413. Solo s/bancarizado (59.2% ventas, excluye efectivo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="24" t="inlineStr">
+        <is>
+          <t>Subtotal impuestos</t>
+        </is>
+      </c>
+      <c r="B71" s="25">
+        <f>B69+B70</f>
+        <v/>
+      </c>
+      <c r="C71" s="27">
+        <f>ABS(B71)/B8</f>
+        <v/>
+      </c>
+      <c r="D71" s="24" t="inlineStr"/>
+      <c r="E71" s="24" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>Ingresos Brutos (Mendoza)</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="n">
-        <v>-331510</v>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>Ley Impositiva Mza 2026, Rubro 7 comercio minorista</t>
-        </is>
-      </c>
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>4.3 MERMA / DESCARTE</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="inlineStr"/>
+      <c r="C73" s="15" t="inlineStr"/>
+      <c r="D73" s="15" t="inlineStr"/>
+      <c r="E73" s="15" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>Imp. Debitos y Creditos Bancarios</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="n">
-        <v>-78465</v>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>0.71%</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>1.2% s/banc.</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>Ley 25.413. Solo s/bancarizado (59.2% ventas, excluye efectivo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="18" t="inlineStr">
-        <is>
-          <t>Subtotal impuestos</t>
-        </is>
-      </c>
-      <c r="B75" s="19" t="n">
-        <v>-409975</v>
-      </c>
-      <c r="C75" s="18" t="inlineStr">
-        <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="D75" s="18" t="inlineStr"/>
-      <c r="E75" s="18" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="13" t="inlineStr">
-        <is>
-          <t>4.3 MERMA / DESCARTE</t>
-        </is>
-      </c>
-      <c r="B77" s="13" t="inlineStr"/>
-      <c r="C77" s="13" t="inlineStr"/>
-      <c r="D77" s="13" t="inlineStr"/>
-      <c r="E77" s="13" t="inlineStr"/>
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>Merma estimada</t>
+        </is>
+      </c>
+      <c r="B74" s="21">
+        <f>-B8*0.05</f>
+        <v/>
+      </c>
+      <c r="C74" s="22">
+        <f>ABS(B74)/B8</f>
+        <v/>
+      </c>
+      <c r="D74" s="20" t="inlineStr"/>
+      <c r="E74" s="20" t="inlineStr">
+        <is>
+          <t>Rotiseria tipico 3-8%. AJUSTAR con dato real</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS VARIABLES</t>
+        </is>
+      </c>
+      <c r="B76" s="11">
+        <f>B66+B71+B74</f>
+        <v/>
+      </c>
+      <c r="C76" s="12">
+        <f>ABS(B76)/B8</f>
+        <v/>
+      </c>
+      <c r="D76" s="10" t="inlineStr"/>
+      <c r="E76" s="10" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="inlineStr">
-        <is>
-          <t>Merma estimada</t>
-        </is>
-      </c>
-      <c r="B78" s="17" t="n">
-        <v>-552517</v>
-      </c>
-      <c r="C78" s="16" t="inlineStr">
-        <is>
-          <t>5.0%</t>
-        </is>
-      </c>
-      <c r="D78" s="16" t="inlineStr"/>
-      <c r="E78" s="16" t="inlineStr">
-        <is>
-          <t>Rotiseria tipico 3-8%. AJUSTAR con dato real</t>
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>5. RESULTADO - MARGEN DE CONTRIBUCION</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Monto Mensual ($)</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>% s/Ventas</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Notas</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>TOTAL COSTOS VARIABLES</t>
-        </is>
-      </c>
-      <c r="B80" s="11" t="n">
-        <v>-1077659</v>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>9.8%</t>
-        </is>
-      </c>
-      <c r="D80" s="10" t="inlineStr"/>
-      <c r="E80" s="10" t="inlineStr"/>
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Ventas Netas</t>
+        </is>
+      </c>
+      <c r="B80" s="6">
+        <f>B8</f>
+        <v/>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr"/>
+      <c r="E80" s="5" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>(-) CMV</t>
+        </is>
+      </c>
+      <c r="B81" s="6">
+        <f>B14</f>
+        <v/>
+      </c>
+      <c r="C81" s="16">
+        <f>ABS(B81)/B80</f>
+        <v/>
+      </c>
+      <c r="D81" s="5" t="inlineStr"/>
+      <c r="E81" s="5" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>5. RESULTADO - MARGEN DE CONTRIBUCION</t>
-        </is>
-      </c>
+      <c r="A82" s="24" t="inlineStr">
+        <is>
+          <t>MARGEN BRUTO</t>
+        </is>
+      </c>
+      <c r="B82" s="25">
+        <f>B80+B81</f>
+        <v/>
+      </c>
+      <c r="C82" s="27">
+        <f>B82/B80</f>
+        <v/>
+      </c>
+      <c r="D82" s="24" t="inlineStr"/>
+      <c r="E82" s="24" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>Concepto</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>Monto Mensual ($)</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>% s/Ventas</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr"/>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>Notas</t>
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>(-) Costos Fijos</t>
+        </is>
+      </c>
+      <c r="B83" s="6">
+        <f>B58</f>
+        <v/>
+      </c>
+      <c r="C83" s="16">
+        <f>ABS(B83)/B80</f>
+        <v/>
+      </c>
+      <c r="D83" s="5" t="inlineStr"/>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Laboral + Servicios + Otros</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Ventas Netas</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="n">
-        <v>11050346</v>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
+          <t>(-) Costos Variables</t>
+        </is>
+      </c>
+      <c r="B84" s="6">
+        <f>B76</f>
+        <v/>
+      </c>
+      <c r="C84" s="16">
+        <f>ABS(B84)/B80</f>
+        <v/>
       </c>
       <c r="D84" s="5" t="inlineStr"/>
       <c r="E84" s="5" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>(-) CMV</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="n">
-        <v>-7735242</v>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>70.0%</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr"/>
-      <c r="E85" s="5" t="inlineStr"/>
+      <c r="A85" s="28" t="inlineStr">
+        <is>
+          <t>RESULTADO NETO</t>
+        </is>
+      </c>
+      <c r="B85" s="29">
+        <f>B82+B83+B84</f>
+        <v/>
+      </c>
+      <c r="C85" s="30">
+        <f>B85/B80</f>
+        <v/>
+      </c>
+      <c r="D85" s="28" t="inlineStr"/>
+      <c r="E85" s="28" t="inlineStr">
+        <is>
+          <t>DEFICITARIO</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="18">
-        <f> MARGEN BRUTO</f>
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Items en amarillo son estimados. Ajustar con datos reales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>6. PUNTO DE EQUILIBRIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="24" t="inlineStr">
+        <is>
+          <t>Ventas necesarias para cubrir costos fijos (margen 30%)</t>
+        </is>
+      </c>
+      <c r="B89" s="25">
+        <f>-B58/(0.3+B76/B8)</f>
         <v/>
       </c>
-      <c r="B86" s="19" t="n">
-        <v>3315104</v>
-      </c>
-      <c r="C86" s="18" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="D86" s="18" t="inlineStr"/>
-      <c r="E86" s="18" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>(-) Costos Fijos</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="n">
-        <v>-5572860</v>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>50.4%</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr"/>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>Laboral + Servicios + Otros</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>(-) Costos Variables</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="n">
-        <v>-1077659</v>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>9.8%</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr"/>
-      <c r="E88" s="5" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="20">
-        <f> MARGEN DE CONTRIBUCION</f>
+      <c r="C89" s="24" t="inlineStr"/>
+      <c r="D89" s="24" t="inlineStr"/>
+      <c r="E89" s="24" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Ventas actuales promedio</t>
+        </is>
+      </c>
+      <c r="B90" s="6">
+        <f>B8</f>
         <v/>
       </c>
-      <c r="B89" s="21" t="n">
-        <v>-3335415</v>
-      </c>
-      <c r="C89" s="20" t="inlineStr">
-        <is>
-          <t>-30.2%</t>
-        </is>
-      </c>
-      <c r="D89" s="20" t="inlineStr"/>
-      <c r="E89" s="20" t="inlineStr">
-        <is>
-          <t>DEFICITARIO</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Items en amarillo son estimados. Ajustar con datos reales.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>6. PUNTO DE EQUILIBRIO</t>
+      <c r="C90" s="5" t="inlineStr"/>
+      <c r="D90" s="5" t="inlineStr"/>
+      <c r="E90" s="5" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>Cobertura punto de equilibrio</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr"/>
+      <c r="C91" s="12">
+        <f>B90/B89</f>
+        <v/>
+      </c>
+      <c r="D91" s="10" t="inlineStr"/>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>INSUFICIENTE</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="18" t="inlineStr">
-        <is>
-          <t>Ventas necesarias para cubrir costos fijos (margen 30%)</t>
-        </is>
-      </c>
-      <c r="B93" s="19" t="n">
-        <v>27523375</v>
-      </c>
-      <c r="C93" s="18" t="inlineStr"/>
-      <c r="D93" s="18" t="inlineStr"/>
-      <c r="E93" s="18" t="inlineStr"/>
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>SUPUESTOS</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>Ventas actuales promedio</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="n">
-        <v>11050346</v>
-      </c>
-      <c r="C94" s="5" t="inlineStr"/>
-      <c r="D94" s="5" t="inlineStr"/>
-      <c r="E94" s="5" t="inlineStr"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Empresa NO inscripta como MiPyME - Contribuciones patronales SUSS al 20.74%</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="10" t="inlineStr">
-        <is>
-          <t>Cobertura punto de equilibrio</t>
-        </is>
-      </c>
-      <c r="B95" s="10" t="inlineStr"/>
-      <c r="C95" s="10" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="D95" s="10" t="inlineStr"/>
-      <c r="E95" s="10" t="inlineStr">
-        <is>
-          <t>INSUFICIENTE</t>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. CCT 130/75 Empleados de Comercio - Categoria Auxiliar Especializado A, sin antiguedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Sueldo: $1,080,274 remunerativo + $100,000 NR = $1,180,274/empleado (escala Dic 2025 - Mar 2026)</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>SUPUESTOS</t>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Contribuciones patronales (29.74%) calculadas SOLO sobre remunerativo. NR no genera cargas</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. Empresa NO inscripta como MiPyME - Contribuciones patronales SUSS al 20.4% (si obtiene certificado MiPyME baja a 18%)</t>
+          <t xml:space="preserve">  5. SAC mensualizado sobre base remunerativa + contribuciones</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. CCT 130/75 Empleados de Comercio - Categoria Auxiliar Especializado A, sin antiguedad</t>
+          <t xml:space="preserve">  6. Margen bruto sobre PVP: 30% (parametro del sistema de facturacion)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Sueldo: $1,080,274 remunerativo + $100,000 NR = $1,180,274/empleado (escala Dic 2025 - Mar 2026)</t>
+          <t xml:space="preserve">  7. Comisiones: Credito 3%, Debito 1.2%, Billetera 1.5% (promedios de mercado)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Contribuciones patronales (29.74%) calculadas SOLO sobre remunerativo. NR no genera cargas</t>
+          <t xml:space="preserve">  8. IIBB Mendoza: 3% (Ley Impositiva Mza 2026, Rubro 7 comercio minorista)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. SAC mensualizado sobre base remunerativa + contribuciones</t>
+          <t xml:space="preserve">  9. Imp. Debitos/Creditos: 1.2% SOLO sobre bancarizado (59.2% ventas). Ley 25.413</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6. Margen bruto sobre PVP: 30% (parametro del sistema de facturacion)</t>
+          <t xml:space="preserve">  10. Merma estimada: 5% (ajustar con medicion real, tipico rotiseria 3-8%)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7. Comisiones: Credito 3%, Debito 1.2%, Billetera 1.5% (promedios de mercado)</t>
+          <t xml:space="preserve">  11. IVA: no se incluye como costo (se compensa DF vs CF). Solo se muestra para referencia</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8. IIBB Mendoza: 3% (Ley Impositiva Mza 2026, Rubro 7 comercio minorista)</t>
+          <t xml:space="preserve">  12. Ventas: ultimos 31 dias reales (16/02/2026 - 18/03/2026) desestacionalizados con indice 2025</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9. Imp. Debitos/Creditos: 1.2% SOLO sobre bancarizado (59.2% ventas). Ley 25.413</t>
+          <t xml:space="preserve">  13. Gas: 332 m3/mes (horno convector + cocina). Factura $664,000/1485m3 compartida con panaderia</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10. Merma estimada: 5% (ajustar con medicion real, tipico rotiseria 3-8%)</t>
+          <t xml:space="preserve">  14. Electricidad: 500 kWh/mes. Tarifa $365.76/kWh all-in s/factura EDEMSA</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11. IVA: no se incluye como costo (se compensa DF vs CF). Solo se muestra para referencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  12. Ventas: ultimos 31 dias reales (16/02/2026 - 18/03/2026) desestacionalizados con indice 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  13. Indice estacional ponderado ventana: 1.0095 (10 meses completos 2025, excl Oct-Nov incompletos)</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  14. Gas: 332 m3/mes estimado (horno convector 8 band. + cocina 2 horn.). Factura compartida con panaderia</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  15. Gas: factura Ecogas Patricios 344 $664,000/1485m3. Rotis 332m3 + Panad 1153m3 = 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  16. Electricidad: 500 kWh/mes estimado (vitrina + heladera insumos + campana + iluminacion)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  17. Electricidad tarifa: $365.76/kWh all-in (s/factura EDEMSA Patricios 334 Mar 2026: $3,463,771/9470kWh, T2 Especial, IVA 27%)</t>
+          <t xml:space="preserve">  15. NO incluye: alquiler, amortizacion equipos, agua, seguros (excluidos por decision del cliente)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="A114:E114"/>
+  <mergeCells count="26">
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
     <mergeCell ref="A98:E98"/>
     <mergeCell ref="A107:E107"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A94:E94"/>
     <mergeCell ref="A103:E103"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A78:E78"/>
     <mergeCell ref="A108:E108"/>
     <mergeCell ref="A99:E99"/>
     <mergeCell ref="A105:E105"/>
     <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A95:E95"/>
     <mergeCell ref="A101:E101"/>
-    <mergeCell ref="A113:E113"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A86:E86"/>
     <mergeCell ref="A104:E104"/>
     <mergeCell ref="A97:E97"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A106:E106"/>
-    <mergeCell ref="A109:E109"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A100:E100"/>
-    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A96:E96"/>
     <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A111:E111"/>
-    <mergeCell ref="A92:E92"/>
+    <mergeCell ref="A93:E93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2345,13 +2280,13 @@
       <c r="F4" s="6" t="n">
         <v>5341683</v>
       </c>
-      <c r="G4" s="22" t="n">
+      <c r="G4" s="31" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>1763566</v>
       </c>
-      <c r="I4" s="22" t="n">
+      <c r="I4" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2376,13 +2311,13 @@
       <c r="F5" s="6" t="n">
         <v>5936779</v>
       </c>
-      <c r="G5" s="22" t="n">
+      <c r="G5" s="31" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>1725885</v>
       </c>
-      <c r="I5" s="22" t="n">
+      <c r="I5" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2407,13 +2342,13 @@
       <c r="F6" s="6" t="n">
         <v>9444356</v>
       </c>
-      <c r="G6" s="22" t="n">
+      <c r="G6" s="31" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>2227234</v>
       </c>
-      <c r="I6" s="22" t="n">
+      <c r="I6" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2754,7 +2689,7 @@
       <c r="H17" s="6" t="n">
         <v>1486911</v>
       </c>
-      <c r="I17" s="22" t="n">
+      <c r="I17" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2785,7 +2720,7 @@
       <c r="H18" s="6" t="n">
         <v>3110419</v>
       </c>
-      <c r="I18" s="22" t="n">
+      <c r="I18" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2816,8 +2751,8 @@
       <c r="H19" s="6" t="n">
         <v>264028</v>
       </c>
-      <c r="I19" s="22" t="n">
-        <v>0</v>
+      <c r="I19" s="6" t="n">
+        <v>1877529</v>
       </c>
     </row>
     <row r="20">
@@ -2844,11 +2779,11 @@
       <c r="G20" s="6" t="n">
         <v>3237470</v>
       </c>
-      <c r="H20" s="22" t="n">
+      <c r="H20" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="22" t="n">
-        <v>0</v>
+      <c r="I20" s="6" t="n">
+        <v>1824484</v>
       </c>
     </row>
     <row r="21">
@@ -2875,11 +2810,11 @@
       <c r="G21" s="6" t="n">
         <v>1883254</v>
       </c>
-      <c r="H21" s="22" t="n">
+      <c r="H21" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="22" t="n">
-        <v>0</v>
+      <c r="I21" s="6" t="n">
+        <v>1542596</v>
       </c>
     </row>
     <row r="23">
@@ -2968,640 +2903,640 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>MATAMBRE NINO</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n">
+      <c r="B4" s="33" t="n">
         <v>21848114</v>
       </c>
-      <c r="C4" s="24" t="n">
+      <c r="C4" s="33" t="n">
         <v>248</v>
       </c>
-      <c r="D4" s="24" t="n">
+      <c r="D4" s="33" t="n">
         <v>35085</v>
       </c>
-      <c r="E4" s="24" t="n">
+      <c r="E4" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="F4" s="24" t="n">
+      <c r="F4" s="33" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>EMPANADA CARNE X 12 UN.</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="33" t="n">
         <v>21267910</v>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="33" t="n">
         <v>2520</v>
       </c>
-      <c r="D5" s="24" t="n">
+      <c r="D5" s="33" t="n">
         <v>8343</v>
       </c>
-      <c r="E5" s="24" t="n">
+      <c r="E5" s="33" t="n">
         <v>13.6</v>
       </c>
-      <c r="F5" s="24" t="n">
+      <c r="F5" s="33" t="n">
         <v>27.6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>EMPANADA CARNE X 6 UN.</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="33" t="n">
         <v>18840000</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="33" t="n">
         <v>4367</v>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="33" t="n">
         <v>4292</v>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="33" t="n">
         <v>12.1</v>
       </c>
-      <c r="F6" s="24" t="n">
+      <c r="F6" s="33" t="n">
         <v>39.7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>EMPANADA J&amp;Q X 6 UN.</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="33" t="n">
         <v>8315100</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="33" t="n">
         <v>1937</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="33" t="n">
         <v>4270</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="33" t="n">
         <v>5.3</v>
       </c>
-      <c r="F7" s="24" t="n">
+      <c r="F7" s="33" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>EMPANADA POLLO X 6 UN.</t>
         </is>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="33" t="n">
         <v>7180250</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="33" t="n">
         <v>1657</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="33" t="n">
         <v>4321</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="33" t="n">
         <v>4.6</v>
       </c>
-      <c r="F8" s="24" t="n">
+      <c r="F8" s="33" t="n">
         <v>49.6</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>LENGUA A LA VINAGRETA NINO</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
+      <c r="B9" s="33" t="n">
         <v>4547066</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="34" t="n">
         <v>54</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="33" t="n">
         <v>16005</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="33" t="n">
         <v>2.9</v>
       </c>
-      <c r="F9" s="24" t="n">
+      <c r="F9" s="33" t="n">
         <v>52.5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>MIGA TRIP. X 12 UNI.</t>
         </is>
       </c>
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="33" t="n">
         <v>4231800</v>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="33" t="n">
         <v>494</v>
       </c>
-      <c r="D10" s="24" t="n">
+      <c r="D10" s="33" t="n">
         <v>8528</v>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="33" t="n">
         <v>2.7</v>
       </c>
-      <c r="F10" s="24" t="n">
+      <c r="F10" s="33" t="n">
         <v>55.2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>EMPANADA VERDURA X 6 UN.</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="33" t="n">
         <v>4124850</v>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="33" t="n">
         <v>965</v>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="33" t="n">
         <v>4257</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="33" t="n">
         <v>2.6</v>
       </c>
-      <c r="F11" s="24" t="n">
+      <c r="F11" s="33" t="n">
         <v>57.9</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>EMPANADA HUMITA X 6 UN.</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="33" t="n">
         <v>3978000</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="33" t="n">
         <v>936</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="33" t="n">
         <v>4241</v>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="33" t="n">
         <v>2.5</v>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="33" t="n">
         <v>60.4</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>PERNIL DE CERDO HORNEADO NINO</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="33" t="n">
         <v>3952006</v>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="34" t="n">
         <v>66</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="33" t="n">
         <v>22047</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="33" t="n">
         <v>2.5</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="33" t="n">
         <v>63</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>PIZZA C/JAMON NINO</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="33" t="n">
         <v>3599100</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="33" t="n">
         <v>446</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="33" t="n">
         <v>7997</v>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="33" t="n">
         <v>2.3</v>
       </c>
-      <c r="F14" s="24" t="n">
+      <c r="F14" s="33" t="n">
         <v>65.3</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>EMPANADA CAPRESE X 6 UN.</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B15" s="33" t="n">
         <v>3584500</v>
       </c>
-      <c r="C15" s="24" t="n">
+      <c r="C15" s="33" t="n">
         <v>834</v>
       </c>
-      <c r="D15" s="24" t="n">
+      <c r="D15" s="33" t="n">
         <v>4262</v>
       </c>
-      <c r="E15" s="24" t="n">
+      <c r="E15" s="33" t="n">
         <v>2.3</v>
       </c>
-      <c r="F15" s="24" t="n">
+      <c r="F15" s="33" t="n">
         <v>67.59999999999999</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>ARROLLADO DE POLLO NINO</t>
         </is>
       </c>
-      <c r="B16" s="24" t="n">
+      <c r="B16" s="33" t="n">
         <v>3516596</v>
       </c>
-      <c r="C16" s="25" t="n">
+      <c r="C16" s="34" t="n">
         <v>72</v>
       </c>
-      <c r="D16" s="24" t="n">
+      <c r="D16" s="33" t="n">
         <v>23536</v>
       </c>
-      <c r="E16" s="24" t="n">
+      <c r="E16" s="33" t="n">
         <v>2.3</v>
       </c>
-      <c r="F16" s="24" t="n">
+      <c r="F16" s="33" t="n">
         <v>69.8</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>CANELONES CAR Y VER NINO</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n">
+      <c r="B17" s="33" t="n">
         <v>3500210</v>
       </c>
-      <c r="C17" s="24" t="n">
+      <c r="C17" s="33" t="n">
         <v>421</v>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="33" t="n">
         <v>10984</v>
       </c>
-      <c r="E17" s="24" t="n">
+      <c r="E17" s="33" t="n">
         <v>2.2</v>
       </c>
-      <c r="F17" s="24" t="n">
+      <c r="F17" s="33" t="n">
         <v>72.09999999999999</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t>PIZZA MUZZARELLA NINO</t>
         </is>
       </c>
-      <c r="B18" s="24" t="n">
+      <c r="B18" s="33" t="n">
         <v>3428000</v>
       </c>
-      <c r="C18" s="24" t="n">
+      <c r="C18" s="33" t="n">
         <v>540</v>
       </c>
-      <c r="D18" s="24" t="n">
+      <c r="D18" s="33" t="n">
         <v>6308</v>
       </c>
-      <c r="E18" s="24" t="n">
+      <c r="E18" s="33" t="n">
         <v>2.2</v>
       </c>
-      <c r="F18" s="24" t="n">
+      <c r="F18" s="33" t="n">
         <v>74.3</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>SALSA BOLOGNESA NINO</t>
         </is>
       </c>
-      <c r="B19" s="24" t="n">
+      <c r="B19" s="33" t="n">
         <v>3291113</v>
       </c>
-      <c r="C19" s="24" t="n">
+      <c r="C19" s="33" t="n">
         <v>476</v>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="33" t="n">
         <v>7335</v>
       </c>
-      <c r="E19" s="24" t="n">
+      <c r="E19" s="33" t="n">
         <v>2.1</v>
       </c>
-      <c r="F19" s="24" t="n">
+      <c r="F19" s="33" t="n">
         <v>76.40000000000001</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>MIGA TRIP. X 6 UNI.</t>
         </is>
       </c>
-      <c r="B20" s="24" t="n">
+      <c r="B20" s="33" t="n">
         <v>3003880</v>
       </c>
-      <c r="C20" s="24" t="n">
+      <c r="C20" s="33" t="n">
         <v>680</v>
       </c>
-      <c r="D20" s="24" t="n">
+      <c r="D20" s="33" t="n">
         <v>4366</v>
       </c>
-      <c r="E20" s="24" t="n">
+      <c r="E20" s="33" t="n">
         <v>1.9</v>
       </c>
-      <c r="F20" s="24" t="n">
+      <c r="F20" s="33" t="n">
         <v>78.3</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>EMPANADA J&amp;Q X 12 UN.</t>
         </is>
       </c>
-      <c r="B21" s="17" t="n">
+      <c r="B21" s="21" t="n">
         <v>2985400</v>
       </c>
-      <c r="C21" s="17" t="n">
+      <c r="C21" s="21" t="n">
         <v>353</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="21" t="n">
         <v>8475</v>
       </c>
-      <c r="E21" s="17" t="n">
+      <c r="E21" s="21" t="n">
         <v>1.9</v>
       </c>
-      <c r="F21" s="17" t="n">
+      <c r="F21" s="21" t="n">
         <v>80.2</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>EMPANADA CEB/QUEX 6 UN.</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n">
+      <c r="B22" s="21" t="n">
         <v>2909900</v>
       </c>
-      <c r="C22" s="17" t="n">
+      <c r="C22" s="21" t="n">
         <v>670</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="21" t="n">
         <v>4317</v>
       </c>
-      <c r="E22" s="17" t="n">
+      <c r="E22" s="21" t="n">
         <v>1.9</v>
       </c>
-      <c r="F22" s="17" t="n">
+      <c r="F22" s="21" t="n">
         <v>82.09999999999999</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>TORTILLA DE PAPA NINO</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B23" s="21" t="n">
         <v>2737178</v>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="35" t="n">
         <v>83</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="21" t="n">
         <v>7284</v>
       </c>
-      <c r="E23" s="17" t="n">
+      <c r="E23" s="21" t="n">
         <v>1.8</v>
       </c>
-      <c r="F23" s="17" t="n">
+      <c r="F23" s="21" t="n">
         <v>83.8</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>PATITAS ALIÑADAS NINO</t>
         </is>
       </c>
-      <c r="B24" s="17" t="n">
+      <c r="B24" s="21" t="n">
         <v>2646077</v>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="35" t="n">
         <v>76</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="21" t="n">
         <v>7533</v>
       </c>
-      <c r="E24" s="17" t="n">
+      <c r="E24" s="21" t="n">
         <v>1.7</v>
       </c>
-      <c r="F24" s="17" t="n">
+      <c r="F24" s="21" t="n">
         <v>85.5</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>ENSALADA RUSA NINO</t>
         </is>
       </c>
-      <c r="B25" s="17" t="n">
+      <c r="B25" s="21" t="n">
         <v>2565688</v>
       </c>
-      <c r="C25" s="17" t="n">
+      <c r="C25" s="21" t="n">
         <v>161</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="21" t="n">
         <v>4397</v>
       </c>
-      <c r="E25" s="17" t="n">
+      <c r="E25" s="21" t="n">
         <v>1.6</v>
       </c>
-      <c r="F25" s="17" t="n">
+      <c r="F25" s="21" t="n">
         <v>87.2</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>ENSALADA MIXTA NINO</t>
         </is>
       </c>
-      <c r="B26" s="17" t="n">
+      <c r="B26" s="21" t="n">
         <v>2369794</v>
       </c>
-      <c r="C26" s="17" t="n">
+      <c r="C26" s="21" t="n">
         <v>224</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="21" t="n">
         <v>4224</v>
       </c>
-      <c r="E26" s="17" t="n">
+      <c r="E26" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="F26" s="17" t="n">
+      <c r="F26" s="21" t="n">
         <v>88.7</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>ROTISERIA</t>
         </is>
       </c>
-      <c r="B27" s="17" t="n">
+      <c r="B27" s="21" t="n">
         <v>2348123</v>
       </c>
-      <c r="C27" s="17" t="n">
+      <c r="C27" s="21" t="n">
         <v>112</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="21" t="n">
         <v>20965</v>
       </c>
-      <c r="E27" s="17" t="n">
+      <c r="E27" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="F27" s="17" t="n">
+      <c r="F27" s="21" t="n">
         <v>90.2</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>ARROZ CON POLLO</t>
         </is>
       </c>
-      <c r="B28" s="17" t="n">
+      <c r="B28" s="21" t="n">
         <v>1409643</v>
       </c>
-      <c r="C28" s="17" t="n">
+      <c r="C28" s="21" t="n">
         <v>284</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="21" t="n">
         <v>7172</v>
       </c>
-      <c r="E28" s="17" t="n">
+      <c r="E28" s="21" t="n">
         <v>0.9</v>
       </c>
-      <c r="F28" s="17" t="n">
+      <c r="F28" s="21" t="n">
         <v>91.09999999999999</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>CANELONES VERD Y RIC NINO</t>
         </is>
       </c>
-      <c r="B29" s="17" t="n">
+      <c r="B29" s="21" t="n">
         <v>1396833</v>
       </c>
-      <c r="C29" s="17" t="n">
+      <c r="C29" s="21" t="n">
         <v>169</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="21" t="n">
         <v>10788</v>
       </c>
-      <c r="E29" s="17" t="n">
+      <c r="E29" s="21" t="n">
         <v>0.9</v>
       </c>
-      <c r="F29" s="17" t="n">
+      <c r="F29" s="21" t="n">
         <v>92</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>EMPANADA ATUN X 6 UN.</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n">
+      <c r="B30" s="21" t="n">
         <v>1375350</v>
       </c>
-      <c r="C30" s="17" t="n">
+      <c r="C30" s="21" t="n">
         <v>282</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="21" t="n">
         <v>4877</v>
       </c>
-      <c r="E30" s="17" t="n">
+      <c r="E30" s="21" t="n">
         <v>0.9</v>
       </c>
-      <c r="F30" s="17" t="n">
+      <c r="F30" s="21" t="n">
         <v>92.90000000000001</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>BERENJENAS EN ESCABECHE NINO</t>
         </is>
       </c>
-      <c r="B31" s="17" t="n">
+      <c r="B31" s="21" t="n">
         <v>1345642</v>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="35" t="n">
         <v>44</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="21" t="n">
         <v>8168</v>
       </c>
-      <c r="E31" s="17" t="n">
+      <c r="E31" s="21" t="n">
         <v>0.9</v>
       </c>
-      <c r="F31" s="17" t="n">
+      <c r="F31" s="21" t="n">
         <v>93.7</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>MIGA TRIPLE X 100 UN.</t>
         </is>
       </c>
-      <c r="B32" s="17" t="n">
+      <c r="B32" s="21" t="n">
         <v>1296900</v>
       </c>
-      <c r="C32" s="26" t="n">
+      <c r="C32" s="35" t="n">
         <v>22</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="21" t="n">
         <v>44907</v>
       </c>
-      <c r="E32" s="17" t="n">
+      <c r="E32" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="F32" s="17" t="n">
+      <c r="F32" s="21" t="n">
         <v>94.59999999999999</v>
       </c>
     </row>
@@ -3614,7 +3549,7 @@
       <c r="B33" s="6" t="n">
         <v>1292645</v>
       </c>
-      <c r="C33" s="22" t="n">
+      <c r="C33" s="31" t="n">
         <v>24</v>
       </c>
       <c r="D33" s="6" t="n">
@@ -3658,7 +3593,7 @@
       <c r="B35" s="6" t="n">
         <v>1189200</v>
       </c>
-      <c r="C35" s="22" t="n">
+      <c r="C35" s="31" t="n">
         <v>92</v>
       </c>
       <c r="D35" s="6" t="n">
@@ -3702,7 +3637,7 @@
       <c r="B37" s="6" t="n">
         <v>626764</v>
       </c>
-      <c r="C37" s="22" t="n">
+      <c r="C37" s="31" t="n">
         <v>25</v>
       </c>
       <c r="D37" s="6" t="n">
@@ -3724,7 +3659,7 @@
       <c r="B38" s="6" t="n">
         <v>606344</v>
       </c>
-      <c r="C38" s="22" t="n">
+      <c r="C38" s="31" t="n">
         <v>7</v>
       </c>
       <c r="D38" s="6" t="n">
@@ -3746,7 +3681,7 @@
       <c r="B39" s="6" t="n">
         <v>455800</v>
       </c>
-      <c r="C39" s="22" t="n">
+      <c r="C39" s="31" t="n">
         <v>58</v>
       </c>
       <c r="D39" s="6" t="n">
@@ -3768,7 +3703,7 @@
       <c r="B40" s="6" t="n">
         <v>289900</v>
       </c>
-      <c r="C40" s="22" t="n">
+      <c r="C40" s="31" t="n">
         <v>35</v>
       </c>
       <c r="D40" s="6" t="n">
@@ -3790,7 +3725,7 @@
       <c r="B41" s="6" t="n">
         <v>188480</v>
       </c>
-      <c r="C41" s="22" t="n">
+      <c r="C41" s="31" t="n">
         <v>11</v>
       </c>
       <c r="D41" s="6" t="n">
@@ -3812,7 +3747,7 @@
       <c r="B42" s="6" t="n">
         <v>180350</v>
       </c>
-      <c r="C42" s="22" t="n">
+      <c r="C42" s="31" t="n">
         <v>46</v>
       </c>
       <c r="D42" s="6" t="n">
@@ -3834,7 +3769,7 @@
       <c r="B43" s="6" t="n">
         <v>170540</v>
       </c>
-      <c r="C43" s="22" t="n">
+      <c r="C43" s="31" t="n">
         <v>37</v>
       </c>
       <c r="D43" s="6" t="n">
@@ -3856,7 +3791,7 @@
       <c r="B44" s="6" t="n">
         <v>159150</v>
       </c>
-      <c r="C44" s="22" t="n">
+      <c r="C44" s="31" t="n">
         <v>12</v>
       </c>
       <c r="D44" s="6" t="n">
@@ -3878,7 +3813,7 @@
       <c r="B45" s="6" t="n">
         <v>128100</v>
       </c>
-      <c r="C45" s="22" t="n">
+      <c r="C45" s="31" t="n">
         <v>14</v>
       </c>
       <c r="D45" s="6" t="n">
@@ -3922,7 +3857,7 @@
       <c r="B47" s="6" t="n">
         <v>122000</v>
       </c>
-      <c r="C47" s="22" t="n">
+      <c r="C47" s="31" t="n">
         <v>2</v>
       </c>
       <c r="D47" s="6" t="n">
@@ -3944,7 +3879,7 @@
       <c r="B48" s="6" t="n">
         <v>100700</v>
       </c>
-      <c r="C48" s="22" t="n">
+      <c r="C48" s="31" t="n">
         <v>45</v>
       </c>
       <c r="D48" s="6" t="n">
@@ -3966,7 +3901,7 @@
       <c r="B49" s="6" t="n">
         <v>83500</v>
       </c>
-      <c r="C49" s="22" t="n">
+      <c r="C49" s="31" t="n">
         <v>38</v>
       </c>
       <c r="D49" s="6" t="n">
@@ -3988,7 +3923,7 @@
       <c r="B50" s="6" t="n">
         <v>83500</v>
       </c>
-      <c r="C50" s="22" t="n">
+      <c r="C50" s="31" t="n">
         <v>10</v>
       </c>
       <c r="D50" s="6" t="n">
@@ -4010,7 +3945,7 @@
       <c r="B51" s="6" t="n">
         <v>79300</v>
       </c>
-      <c r="C51" s="22" t="n">
+      <c r="C51" s="31" t="n">
         <v>36</v>
       </c>
       <c r="D51" s="6" t="n">
@@ -4032,7 +3967,7 @@
       <c r="B52" s="6" t="n">
         <v>77342</v>
       </c>
-      <c r="C52" s="22" t="n">
+      <c r="C52" s="31" t="n">
         <v>1</v>
       </c>
       <c r="D52" s="6" t="n">
@@ -4054,7 +3989,7 @@
       <c r="B53" s="6" t="n">
         <v>76800</v>
       </c>
-      <c r="C53" s="22" t="n">
+      <c r="C53" s="31" t="n">
         <v>8</v>
       </c>
       <c r="D53" s="6" t="n">
@@ -4076,7 +4011,7 @@
       <c r="B54" s="6" t="n">
         <v>59650</v>
       </c>
-      <c r="C54" s="22" t="n">
+      <c r="C54" s="31" t="n">
         <v>26</v>
       </c>
       <c r="D54" s="6" t="n">
@@ -4098,7 +4033,7 @@
       <c r="B55" s="6" t="n">
         <v>52200</v>
       </c>
-      <c r="C55" s="22" t="n">
+      <c r="C55" s="31" t="n">
         <v>6</v>
       </c>
       <c r="D55" s="6" t="n">
@@ -4120,7 +4055,7 @@
       <c r="B56" s="6" t="n">
         <v>51700</v>
       </c>
-      <c r="C56" s="22" t="n">
+      <c r="C56" s="31" t="n">
         <v>23</v>
       </c>
       <c r="D56" s="6" t="n">
@@ -4142,7 +4077,7 @@
       <c r="B57" s="6" t="n">
         <v>45100</v>
       </c>
-      <c r="C57" s="22" t="n">
+      <c r="C57" s="31" t="n">
         <v>19</v>
       </c>
       <c r="D57" s="6" t="n">
@@ -4164,7 +4099,7 @@
       <c r="B58" s="6" t="n">
         <v>40600</v>
       </c>
-      <c r="C58" s="22" t="n">
+      <c r="C58" s="31" t="n">
         <v>28</v>
       </c>
       <c r="D58" s="6" t="n">
@@ -4186,7 +4121,7 @@
       <c r="B59" s="6" t="n">
         <v>37550</v>
       </c>
-      <c r="C59" s="22" t="n">
+      <c r="C59" s="31" t="n">
         <v>17</v>
       </c>
       <c r="D59" s="6" t="n">
@@ -4208,7 +4143,7 @@
       <c r="B60" s="6" t="n">
         <v>35800</v>
       </c>
-      <c r="C60" s="22" t="n">
+      <c r="C60" s="31" t="n">
         <v>1</v>
       </c>
       <c r="D60" s="6" t="n">
@@ -4230,7 +4165,7 @@
       <c r="B61" s="6" t="n">
         <v>21000</v>
       </c>
-      <c r="C61" s="22" t="n">
+      <c r="C61" s="31" t="n">
         <v>2</v>
       </c>
       <c r="D61" s="6" t="n">
@@ -4252,7 +4187,7 @@
       <c r="B62" s="6" t="n">
         <v>19200</v>
       </c>
-      <c r="C62" s="22" t="n">
+      <c r="C62" s="31" t="n">
         <v>9</v>
       </c>
       <c r="D62" s="6" t="n">
@@ -4274,7 +4209,7 @@
       <c r="B63" s="6" t="n">
         <v>14900</v>
       </c>
-      <c r="C63" s="22" t="n">
+      <c r="C63" s="31" t="n">
         <v>20</v>
       </c>
       <c r="D63" s="6" t="n">
@@ -4296,7 +4231,7 @@
       <c r="B64" s="6" t="n">
         <v>6500</v>
       </c>
-      <c r="C64" s="22" t="n">
+      <c r="C64" s="31" t="n">
         <v>8</v>
       </c>
       <c r="D64" s="6" t="n">
@@ -4318,7 +4253,7 @@
       <c r="B65" s="6" t="n">
         <v>5900</v>
       </c>
-      <c r="C65" s="22" t="n">
+      <c r="C65" s="31" t="n">
         <v>8</v>
       </c>
       <c r="D65" s="6" t="n">
@@ -4340,7 +4275,7 @@
       <c r="B66" s="6" t="n">
         <v>4050</v>
       </c>
-      <c r="C66" s="22" t="n">
+      <c r="C66" s="31" t="n">
         <v>1</v>
       </c>
       <c r="D66" s="6" t="n">
@@ -4362,7 +4297,7 @@
       <c r="B67" s="6" t="n">
         <v>218</v>
       </c>
-      <c r="C67" s="22" t="n">
+      <c r="C67" s="31" t="n">
         <v>0</v>
       </c>
       <c r="D67" s="6" t="n">
@@ -4420,7 +4355,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Precios insumos: sistema POS supermercado NINO × 0.70 (costo mayorista estimado) | Validacion del margen 30%</t>
+          <t>Precios insumos: sistema POS supermercado NINO x 0.70 (costo mayorista estimado)</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4384,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Costo Est. (×0.70)</t>
+          <t>Costo Est. (x0.70)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -4467,7 +4402,7 @@
           <t>Carne picada especial</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="13" t="n">
         <v>12200</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -4475,7 +4410,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="13" t="n">
         <v>8540</v>
       </c>
       <c r="E6" s="9" t="inlineStr"/>
@@ -4493,7 +4428,7 @@
           <t>Matambre vacuno crudo</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="13" t="n">
         <v>18020</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -4501,7 +4436,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="13" t="n">
         <v>12614</v>
       </c>
       <c r="E7" s="9" t="inlineStr"/>
@@ -4519,7 +4454,7 @@
           <t>Pollo entero</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
         <v>3900</v>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -4527,7 +4462,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="13" t="n">
         <v>2730</v>
       </c>
       <c r="E8" s="9" t="inlineStr"/>
@@ -4545,7 +4480,7 @@
           <t>Suprema pollo</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <v>10595</v>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -4553,7 +4488,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="13" t="n">
         <v>7416</v>
       </c>
       <c r="E9" s="9" t="inlineStr"/>
@@ -4571,7 +4506,7 @@
           <t>Pernil chancho cong.</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <v>4500</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -4579,7 +4514,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="13" t="n">
         <v>3150</v>
       </c>
       <c r="E10" s="9" t="inlineStr"/>
@@ -4597,7 +4532,7 @@
           <t>Lengua vacuna</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="13" t="n">
         <v>10150</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -4605,7 +4540,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="13" t="n">
         <v>7105</v>
       </c>
       <c r="E11" s="9" t="inlineStr"/>
@@ -4623,7 +4558,7 @@
           <t>Nalga/bola lomo</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="13" t="n">
         <v>13400</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -4631,7 +4566,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="13" t="n">
         <v>9380</v>
       </c>
       <c r="E12" s="9" t="inlineStr"/>
@@ -4649,7 +4584,7 @@
           <t>Jamon cocido</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>18525</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -4657,7 +4592,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="13" t="n">
         <v>12968</v>
       </c>
       <c r="E13" s="9" t="inlineStr"/>
@@ -4675,7 +4610,7 @@
           <t>Muzzarella horma</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="13" t="n">
         <v>7300</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -4683,7 +4618,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="13" t="n">
         <v>5110</v>
       </c>
       <c r="E14" s="9" t="inlineStr"/>
@@ -4701,7 +4636,7 @@
           <t>Tapas empanada x12</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="13" t="n">
         <v>1300</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -4709,7 +4644,7 @@
           <t>$/doc</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="13" t="n">
         <v>910</v>
       </c>
       <c r="E15" s="9" t="inlineStr"/>
@@ -4727,7 +4662,7 @@
           <t>Tapas miga x50</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="13" t="n">
         <v>15360</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -4735,7 +4670,7 @@
           <t>$/pack</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="13" t="n">
         <v>10752</v>
       </c>
       <c r="E16" s="9" t="inlineStr"/>
@@ -4753,7 +4688,7 @@
           <t>Harina 0000</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="13" t="n">
         <v>980</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -4761,7 +4696,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="13" t="n">
         <v>686</v>
       </c>
       <c r="E17" s="9" t="inlineStr"/>
@@ -4779,7 +4714,7 @@
           <t>Huevos x6</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="13" t="n">
         <v>1750</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -4787,7 +4722,7 @@
           <t>$/pack</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="13" t="n">
         <v>1225</v>
       </c>
       <c r="E18" s="9" t="inlineStr"/>
@@ -4805,7 +4740,7 @@
           <t>Pan rallado</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="13" t="n">
         <v>3130</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -4813,7 +4748,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="13" t="n">
         <v>2191</v>
       </c>
       <c r="E19" s="9" t="inlineStr"/>
@@ -4831,7 +4766,7 @@
           <t>Aceite girasol 900ml</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="13" t="n">
         <v>2750</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -4839,7 +4774,7 @@
           <t>$/u</t>
         </is>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="13" t="n">
         <v>1925</v>
       </c>
       <c r="E20" s="9" t="inlineStr"/>
@@ -4854,10 +4789,10 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Puré tomate 520g</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="n">
+          <t>Pure tomate 520g</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
         <v>785</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -4865,7 +4800,7 @@
           <t>$/u</t>
         </is>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" s="13" t="n">
         <v>550</v>
       </c>
       <c r="E21" s="9" t="inlineStr"/>
@@ -4907,7 +4842,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Costo (×0.70)</t>
+          <t>Costo (x0.70)</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -4927,20 +4862,20 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>EMPANADA CARNE x12</t>
         </is>
       </c>
-      <c r="B25" s="27" t="inlineStr"/>
-      <c r="C25" s="27" t="inlineStr"/>
-      <c r="D25" s="27" t="inlineStr"/>
-      <c r="E25" s="27" t="inlineStr"/>
-      <c r="F25" s="28" t="n">
+      <c r="B25" s="36" t="inlineStr"/>
+      <c r="C25" s="36" t="inlineStr"/>
+      <c r="D25" s="36" t="inlineStr"/>
+      <c r="E25" s="36" t="inlineStr"/>
+      <c r="F25" s="37" t="n">
         <v>8000</v>
       </c>
-      <c r="G25" s="27" t="inlineStr"/>
-      <c r="H25" s="27" t="inlineStr">
+      <c r="G25" s="36" t="inlineStr"/>
+      <c r="H25" s="36" t="inlineStr">
         <is>
           <t>49.8%</t>
         </is>
@@ -4952,7 +4887,7 @@
           <t xml:space="preserve">  Carne picada especial</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="13" t="n">
         <v>0.35</v>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -4960,10 +4895,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="D26" s="13" t="n">
         <v>4270</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="13" t="n">
         <v>2989</v>
       </c>
       <c r="F26" s="9" t="inlineStr"/>
@@ -4976,7 +4911,7 @@
           <t xml:space="preserve">  Tapas empanada x12</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="38" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -4984,10 +4919,10 @@
           <t>doc</t>
         </is>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="D27" s="13" t="n">
         <v>1300</v>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="13" t="n">
         <v>910</v>
       </c>
       <c r="F27" s="9" t="inlineStr"/>
@@ -5000,7 +4935,7 @@
           <t xml:space="preserve">  Cebolla</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="13" t="n">
         <v>0.15</v>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -5008,10 +4943,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="D28" s="13" t="n">
         <v>225</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="13" t="n">
         <v>158</v>
       </c>
       <c r="F28" s="9" t="inlineStr"/>
@@ -5024,7 +4959,7 @@
           <t xml:space="preserve">  Huevo (1/2)</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="13" t="n">
         <v>0.5</v>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -5032,10 +4967,10 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="D29" s="13" t="n">
         <v>146</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="13" t="n">
         <v>102</v>
       </c>
       <c r="F29" s="9" t="inlineStr"/>
@@ -5048,7 +4983,7 @@
           <t xml:space="preserve">  Condimentos/grasa</t>
         </is>
       </c>
-      <c r="B30" s="29" t="n">
+      <c r="B30" s="38" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -5056,10 +4991,10 @@
           <t>lote</t>
         </is>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="D30" s="13" t="n">
         <v>300</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="13" t="n">
         <v>210</v>
       </c>
       <c r="F30" s="9" t="inlineStr"/>
@@ -5089,20 +5024,20 @@
       <c r="H31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>EMPANADA J&amp;Q x6</t>
         </is>
       </c>
-      <c r="B32" s="27" t="inlineStr"/>
-      <c r="C32" s="27" t="inlineStr"/>
-      <c r="D32" s="27" t="inlineStr"/>
-      <c r="E32" s="27" t="inlineStr"/>
-      <c r="F32" s="28" t="n">
+      <c r="B32" s="36" t="inlineStr"/>
+      <c r="C32" s="36" t="inlineStr"/>
+      <c r="D32" s="36" t="inlineStr"/>
+      <c r="E32" s="36" t="inlineStr"/>
+      <c r="F32" s="37" t="n">
         <v>4058</v>
       </c>
-      <c r="G32" s="27" t="inlineStr"/>
-      <c r="H32" s="27" t="inlineStr">
+      <c r="G32" s="36" t="inlineStr"/>
+      <c r="H32" s="36" t="inlineStr">
         <is>
           <t>5.2%</t>
         </is>
@@ -5114,7 +5049,7 @@
           <t xml:space="preserve">  Jamon cocido</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="13" t="n">
         <v>0.12</v>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -5122,10 +5057,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D33" s="12" t="n">
+      <c r="D33" s="13" t="n">
         <v>2223</v>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="13" t="n">
         <v>1556</v>
       </c>
       <c r="F33" s="9" t="inlineStr"/>
@@ -5138,7 +5073,7 @@
           <t xml:space="preserve">  Muzzarella</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n">
+      <c r="B34" s="13" t="n">
         <v>0.1</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -5146,10 +5081,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D34" s="12" t="n">
+      <c r="D34" s="13" t="n">
         <v>730</v>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="13" t="n">
         <v>511</v>
       </c>
       <c r="F34" s="9" t="inlineStr"/>
@@ -5162,7 +5097,7 @@
           <t xml:space="preserve">  Tapas empanada x6</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="13" t="n">
         <v>0.5</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -5170,10 +5105,10 @@
           <t>doc</t>
         </is>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="D35" s="13" t="n">
         <v>650</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="13" t="n">
         <v>455</v>
       </c>
       <c r="F35" s="9" t="inlineStr"/>
@@ -5186,7 +5121,7 @@
           <t xml:space="preserve">  Condimentos</t>
         </is>
       </c>
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="38" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -5194,10 +5129,10 @@
           <t>lote</t>
         </is>
       </c>
-      <c r="D36" s="12" t="n">
+      <c r="D36" s="13" t="n">
         <v>150</v>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="13" t="n">
         <v>105</v>
       </c>
       <c r="F36" s="9" t="inlineStr"/>
@@ -5227,20 +5162,20 @@
       <c r="H37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="27" t="inlineStr">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>MATAMBRE NINO (pieza)</t>
         </is>
       </c>
-      <c r="B38" s="27" t="inlineStr"/>
-      <c r="C38" s="27" t="inlineStr"/>
-      <c r="D38" s="27" t="inlineStr"/>
-      <c r="E38" s="27" t="inlineStr"/>
-      <c r="F38" s="28" t="n">
+      <c r="B38" s="36" t="inlineStr"/>
+      <c r="C38" s="36" t="inlineStr"/>
+      <c r="D38" s="36" t="inlineStr"/>
+      <c r="E38" s="36" t="inlineStr"/>
+      <c r="F38" s="37" t="n">
         <v>38200</v>
       </c>
-      <c r="G38" s="27" t="inlineStr"/>
-      <c r="H38" s="27" t="inlineStr">
+      <c r="G38" s="36" t="inlineStr"/>
+      <c r="H38" s="36" t="inlineStr">
         <is>
           <t>13.9%</t>
         </is>
@@ -5252,7 +5187,7 @@
           <t xml:space="preserve">  Matambre vacuno crudo</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="13" t="n">
         <v>1.8</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -5260,10 +5195,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D39" s="13" t="n">
         <v>32436</v>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="13" t="n">
         <v>22705</v>
       </c>
       <c r="F39" s="9" t="inlineStr"/>
@@ -5276,7 +5211,7 @@
           <t xml:space="preserve">  Condimentos/vinagre</t>
         </is>
       </c>
-      <c r="B40" s="29" t="n">
+      <c r="B40" s="38" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -5284,10 +5219,10 @@
           <t>lote</t>
         </is>
       </c>
-      <c r="D40" s="12" t="n">
+      <c r="D40" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="13" t="n">
         <v>350</v>
       </c>
       <c r="F40" s="9" t="inlineStr"/>
@@ -5317,20 +5252,20 @@
       <c r="H41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="27" t="inlineStr">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>PIZZA MUZZARELLA</t>
         </is>
       </c>
-      <c r="B42" s="27" t="inlineStr"/>
-      <c r="C42" s="27" t="inlineStr"/>
-      <c r="D42" s="27" t="inlineStr"/>
-      <c r="E42" s="27" t="inlineStr"/>
-      <c r="F42" s="28" t="n">
+      <c r="B42" s="36" t="inlineStr"/>
+      <c r="C42" s="36" t="inlineStr"/>
+      <c r="D42" s="36" t="inlineStr"/>
+      <c r="E42" s="36" t="inlineStr"/>
+      <c r="F42" s="37" t="n">
         <v>6900</v>
       </c>
-      <c r="G42" s="27" t="inlineStr"/>
-      <c r="H42" s="27" t="inlineStr">
+      <c r="G42" s="36" t="inlineStr"/>
+      <c r="H42" s="36" t="inlineStr">
         <is>
           <t>2.2%</t>
         </is>
@@ -5342,7 +5277,7 @@
           <t xml:space="preserve">  Harina 0000</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="13" t="n">
         <v>0.25</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
@@ -5350,10 +5285,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D43" s="12" t="n">
+      <c r="D43" s="13" t="n">
         <v>245</v>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="13" t="n">
         <v>172</v>
       </c>
       <c r="F43" s="9" t="inlineStr"/>
@@ -5366,7 +5301,7 @@
           <t xml:space="preserve">  Muzzarella</t>
         </is>
       </c>
-      <c r="B44" s="12" t="n">
+      <c r="B44" s="13" t="n">
         <v>0.2</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
@@ -5374,10 +5309,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D44" s="12" t="n">
+      <c r="D44" s="13" t="n">
         <v>1460</v>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="13" t="n">
         <v>1022</v>
       </c>
       <c r="F44" s="9" t="inlineStr"/>
@@ -5390,7 +5325,7 @@
           <t xml:space="preserve">  Salsa tomate</t>
         </is>
       </c>
-      <c r="B45" s="12" t="n">
+      <c r="B45" s="13" t="n">
         <v>0.15</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
@@ -5398,10 +5333,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D45" s="12" t="n">
+      <c r="D45" s="13" t="n">
         <v>226</v>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="13" t="n">
         <v>159</v>
       </c>
       <c r="F45" s="9" t="inlineStr"/>
@@ -5414,7 +5349,7 @@
           <t xml:space="preserve">  Levadura/sal/aceite</t>
         </is>
       </c>
-      <c r="B46" s="29" t="n">
+      <c r="B46" s="38" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
@@ -5422,10 +5357,10 @@
           <t>lote</t>
         </is>
       </c>
-      <c r="D46" s="12" t="n">
+      <c r="D46" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="13" t="n">
         <v>140</v>
       </c>
       <c r="F46" s="9" t="inlineStr"/>
@@ -5455,20 +5390,20 @@
       <c r="H47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="27" t="inlineStr">
+      <c r="A48" s="36" t="inlineStr">
         <is>
           <t>CANELONES CAR/VER (u)</t>
         </is>
       </c>
-      <c r="B48" s="27" t="inlineStr"/>
-      <c r="C48" s="27" t="inlineStr"/>
-      <c r="D48" s="27" t="inlineStr"/>
-      <c r="E48" s="27" t="inlineStr"/>
-      <c r="F48" s="28" t="n">
+      <c r="B48" s="36" t="inlineStr"/>
+      <c r="C48" s="36" t="inlineStr"/>
+      <c r="D48" s="36" t="inlineStr"/>
+      <c r="E48" s="36" t="inlineStr"/>
+      <c r="F48" s="37" t="n">
         <v>10329</v>
       </c>
-      <c r="G48" s="27" t="inlineStr"/>
-      <c r="H48" s="27" t="inlineStr">
+      <c r="G48" s="36" t="inlineStr"/>
+      <c r="H48" s="36" t="inlineStr">
         <is>
           <t>2.2%</t>
         </is>
@@ -5480,7 +5415,7 @@
           <t xml:space="preserve">  Carne picada</t>
         </is>
       </c>
-      <c r="B49" s="12" t="n">
+      <c r="B49" s="13" t="n">
         <v>0.15</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
@@ -5488,10 +5423,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D49" s="12" t="n">
+      <c r="D49" s="13" t="n">
         <v>1830</v>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E49" s="13" t="n">
         <v>1281</v>
       </c>
       <c r="F49" s="9" t="inlineStr"/>
@@ -5504,7 +5439,7 @@
           <t xml:space="preserve">  Tapas canelones/masa</t>
         </is>
       </c>
-      <c r="B50" s="29" t="n">
+      <c r="B50" s="38" t="n">
         <v>1</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
@@ -5512,10 +5447,10 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D50" s="12" t="n">
+      <c r="D50" s="13" t="n">
         <v>800</v>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E50" s="13" t="n">
         <v>560</v>
       </c>
       <c r="F50" s="9" t="inlineStr"/>
@@ -5528,7 +5463,7 @@
           <t xml:space="preserve">  Ricota/verdura</t>
         </is>
       </c>
-      <c r="B51" s="12" t="n">
+      <c r="B51" s="13" t="n">
         <v>0.15</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
@@ -5536,10 +5471,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="D51" s="13" t="n">
         <v>982</v>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="13" t="n">
         <v>688</v>
       </c>
       <c r="F51" s="9" t="inlineStr"/>
@@ -5552,7 +5487,7 @@
           <t xml:space="preserve">  Salsa tomate</t>
         </is>
       </c>
-      <c r="B52" s="12" t="n">
+      <c r="B52" s="13" t="n">
         <v>0.2</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
@@ -5560,10 +5495,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D52" s="12" t="n">
+      <c r="D52" s="13" t="n">
         <v>302</v>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="E52" s="13" t="n">
         <v>211</v>
       </c>
       <c r="F52" s="9" t="inlineStr"/>
@@ -5576,7 +5511,7 @@
           <t xml:space="preserve">  Muzzarella</t>
         </is>
       </c>
-      <c r="B53" s="12" t="n">
+      <c r="B53" s="13" t="n">
         <v>0.08</v>
       </c>
       <c r="C53" s="9" t="inlineStr">
@@ -5584,10 +5519,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D53" s="12" t="n">
+      <c r="D53" s="13" t="n">
         <v>584</v>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="E53" s="13" t="n">
         <v>409</v>
       </c>
       <c r="F53" s="9" t="inlineStr"/>
@@ -5617,20 +5552,20 @@
       <c r="H54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="27" t="inlineStr">
+      <c r="A55" s="36" t="inlineStr">
         <is>
           <t>LENGUA VINAGRETA (pieza)</t>
         </is>
       </c>
-      <c r="B55" s="27" t="inlineStr"/>
-      <c r="C55" s="27" t="inlineStr"/>
-      <c r="D55" s="27" t="inlineStr"/>
-      <c r="E55" s="27" t="inlineStr"/>
-      <c r="F55" s="28" t="n">
+      <c r="B55" s="36" t="inlineStr"/>
+      <c r="C55" s="36" t="inlineStr"/>
+      <c r="D55" s="36" t="inlineStr"/>
+      <c r="E55" s="36" t="inlineStr"/>
+      <c r="F55" s="37" t="n">
         <v>19000</v>
       </c>
-      <c r="G55" s="27" t="inlineStr"/>
-      <c r="H55" s="27" t="inlineStr">
+      <c r="G55" s="36" t="inlineStr"/>
+      <c r="H55" s="36" t="inlineStr">
         <is>
           <t>2.9%</t>
         </is>
@@ -5642,7 +5577,7 @@
           <t xml:space="preserve">  Lengua vacuna</t>
         </is>
       </c>
-      <c r="B56" s="12" t="n">
+      <c r="B56" s="13" t="n">
         <v>1.5</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
@@ -5650,10 +5585,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D56" s="12" t="n">
+      <c r="D56" s="13" t="n">
         <v>15225</v>
       </c>
-      <c r="E56" s="12" t="n">
+      <c r="E56" s="13" t="n">
         <v>10658</v>
       </c>
       <c r="F56" s="9" t="inlineStr"/>
@@ -5666,7 +5601,7 @@
           <t xml:space="preserve">  Vinagre/condimentos</t>
         </is>
       </c>
-      <c r="B57" s="29" t="n">
+      <c r="B57" s="38" t="n">
         <v>1</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
@@ -5674,10 +5609,10 @@
           <t>lote</t>
         </is>
       </c>
-      <c r="D57" s="12" t="n">
+      <c r="D57" s="13" t="n">
         <v>800</v>
       </c>
-      <c r="E57" s="12" t="n">
+      <c r="E57" s="13" t="n">
         <v>560</v>
       </c>
       <c r="F57" s="9" t="inlineStr"/>
@@ -5707,20 +5642,20 @@
       <c r="H58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="27" t="inlineStr">
+      <c r="A59" s="36" t="inlineStr">
         <is>
           <t>PERNIL CERDO (pieza)</t>
         </is>
       </c>
-      <c r="B59" s="27" t="inlineStr"/>
-      <c r="C59" s="27" t="inlineStr"/>
-      <c r="D59" s="27" t="inlineStr"/>
-      <c r="E59" s="27" t="inlineStr"/>
-      <c r="F59" s="28" t="n">
+      <c r="B59" s="36" t="inlineStr"/>
+      <c r="C59" s="36" t="inlineStr"/>
+      <c r="D59" s="36" t="inlineStr"/>
+      <c r="E59" s="36" t="inlineStr"/>
+      <c r="F59" s="37" t="n">
         <v>20477</v>
       </c>
-      <c r="G59" s="27" t="inlineStr"/>
-      <c r="H59" s="27" t="inlineStr">
+      <c r="G59" s="36" t="inlineStr"/>
+      <c r="H59" s="36" t="inlineStr">
         <is>
           <t>2.4%</t>
         </is>
@@ -5732,7 +5667,7 @@
           <t xml:space="preserve">  Pernil chancho congelado</t>
         </is>
       </c>
-      <c r="B60" s="12" t="n">
+      <c r="B60" s="13" t="n">
         <v>3</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
@@ -5740,10 +5675,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D60" s="12" t="n">
+      <c r="D60" s="13" t="n">
         <v>13500</v>
       </c>
-      <c r="E60" s="12" t="n">
+      <c r="E60" s="13" t="n">
         <v>9450</v>
       </c>
       <c r="F60" s="9" t="inlineStr"/>
@@ -5756,7 +5691,7 @@
           <t xml:space="preserve">  Condimentos/adobo</t>
         </is>
       </c>
-      <c r="B61" s="29" t="n">
+      <c r="B61" s="38" t="n">
         <v>1</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
@@ -5764,10 +5699,10 @@
           <t>lote</t>
         </is>
       </c>
-      <c r="D61" s="12" t="n">
+      <c r="D61" s="13" t="n">
         <v>800</v>
       </c>
-      <c r="E61" s="12" t="n">
+      <c r="E61" s="13" t="n">
         <v>560</v>
       </c>
       <c r="F61" s="9" t="inlineStr"/>
@@ -5797,20 +5732,20 @@
       <c r="H62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="27" t="inlineStr">
+      <c r="A63" s="36" t="inlineStr">
         <is>
           <t>ARROLLADO POLLO (pieza)</t>
         </is>
       </c>
-      <c r="B63" s="27" t="inlineStr"/>
-      <c r="C63" s="27" t="inlineStr"/>
-      <c r="D63" s="27" t="inlineStr"/>
-      <c r="E63" s="27" t="inlineStr"/>
-      <c r="F63" s="28" t="n">
+      <c r="B63" s="36" t="inlineStr"/>
+      <c r="C63" s="36" t="inlineStr"/>
+      <c r="D63" s="36" t="inlineStr"/>
+      <c r="E63" s="36" t="inlineStr"/>
+      <c r="F63" s="37" t="n">
         <v>22461</v>
       </c>
-      <c r="G63" s="27" t="inlineStr"/>
-      <c r="H63" s="27" t="inlineStr">
+      <c r="G63" s="36" t="inlineStr"/>
+      <c r="H63" s="36" t="inlineStr">
         <is>
           <t>2.4%</t>
         </is>
@@ -5822,7 +5757,7 @@
           <t xml:space="preserve">  Suprema pollo</t>
         </is>
       </c>
-      <c r="B64" s="12" t="n">
+      <c r="B64" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
@@ -5830,10 +5765,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D64" s="12" t="n">
+      <c r="D64" s="13" t="n">
         <v>10595</v>
       </c>
-      <c r="E64" s="12" t="n">
+      <c r="E64" s="13" t="n">
         <v>7416</v>
       </c>
       <c r="F64" s="9" t="inlineStr"/>
@@ -5846,7 +5781,7 @@
           <t xml:space="preserve">  Jamon/queso relleno</t>
         </is>
       </c>
-      <c r="B65" s="12" t="n">
+      <c r="B65" s="13" t="n">
         <v>0.15</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
@@ -5854,10 +5789,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D65" s="12" t="n">
+      <c r="D65" s="13" t="n">
         <v>2779</v>
       </c>
-      <c r="E65" s="12" t="n">
+      <c r="E65" s="13" t="n">
         <v>1945</v>
       </c>
       <c r="F65" s="9" t="inlineStr"/>
@@ -5870,7 +5805,7 @@
           <t xml:space="preserve">  Condimentos</t>
         </is>
       </c>
-      <c r="B66" s="29" t="n">
+      <c r="B66" s="38" t="n">
         <v>1</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
@@ -5878,10 +5813,10 @@
           <t>lote</t>
         </is>
       </c>
-      <c r="D66" s="12" t="n">
+      <c r="D66" s="13" t="n">
         <v>400</v>
       </c>
-      <c r="E66" s="12" t="n">
+      <c r="E66" s="13" t="n">
         <v>280</v>
       </c>
       <c r="F66" s="9" t="inlineStr"/>
@@ -5911,20 +5846,20 @@
       <c r="H67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="27" t="inlineStr">
+      <c r="A68" s="36" t="inlineStr">
         <is>
           <t>MILANESA MIGA x12</t>
         </is>
       </c>
-      <c r="B68" s="27" t="inlineStr"/>
-      <c r="C68" s="27" t="inlineStr"/>
-      <c r="D68" s="27" t="inlineStr"/>
-      <c r="E68" s="27" t="inlineStr"/>
-      <c r="F68" s="28" t="n">
+      <c r="B68" s="36" t="inlineStr"/>
+      <c r="C68" s="36" t="inlineStr"/>
+      <c r="D68" s="36" t="inlineStr"/>
+      <c r="E68" s="36" t="inlineStr"/>
+      <c r="F68" s="37" t="n">
         <v>8304</v>
       </c>
-      <c r="G68" s="27" t="inlineStr"/>
-      <c r="H68" s="27" t="inlineStr">
+      <c r="G68" s="36" t="inlineStr"/>
+      <c r="H68" s="36" t="inlineStr">
         <is>
           <t>2.6%</t>
         </is>
@@ -5936,7 +5871,7 @@
           <t xml:space="preserve">  Nalga/bola lomo</t>
         </is>
       </c>
-      <c r="B69" s="12" t="n">
+      <c r="B69" s="13" t="n">
         <v>0.8</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
@@ -5944,10 +5879,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D69" s="12" t="n">
+      <c r="D69" s="13" t="n">
         <v>10720</v>
       </c>
-      <c r="E69" s="12" t="n">
+      <c r="E69" s="13" t="n">
         <v>7504</v>
       </c>
       <c r="F69" s="9" t="inlineStr"/>
@@ -5960,7 +5895,7 @@
           <t xml:space="preserve">  Pan rallado</t>
         </is>
       </c>
-      <c r="B70" s="12" t="n">
+      <c r="B70" s="13" t="n">
         <v>0.15</v>
       </c>
       <c r="C70" s="9" t="inlineStr">
@@ -5968,10 +5903,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D70" s="12" t="n">
+      <c r="D70" s="13" t="n">
         <v>470</v>
       </c>
-      <c r="E70" s="12" t="n">
+      <c r="E70" s="13" t="n">
         <v>329</v>
       </c>
       <c r="F70" s="9" t="inlineStr"/>
@@ -5984,7 +5919,7 @@
           <t xml:space="preserve">  Huevos x2</t>
         </is>
       </c>
-      <c r="B71" s="29" t="n">
+      <c r="B71" s="38" t="n">
         <v>2</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -5992,10 +5927,10 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D71" s="12" t="n">
+      <c r="D71" s="13" t="n">
         <v>584</v>
       </c>
-      <c r="E71" s="12" t="n">
+      <c r="E71" s="13" t="n">
         <v>409</v>
       </c>
       <c r="F71" s="9" t="inlineStr"/>
@@ -6008,7 +5943,7 @@
           <t xml:space="preserve">  Tapas miga x12</t>
         </is>
       </c>
-      <c r="B72" s="12" t="n">
+      <c r="B72" s="13" t="n">
         <v>0.24</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
@@ -6016,10 +5951,10 @@
           <t>pack50</t>
         </is>
       </c>
-      <c r="D72" s="12" t="n">
+      <c r="D72" s="13" t="n">
         <v>3686</v>
       </c>
-      <c r="E72" s="12" t="n">
+      <c r="E72" s="13" t="n">
         <v>2580</v>
       </c>
       <c r="F72" s="9" t="inlineStr"/>
@@ -6049,20 +5984,20 @@
       <c r="H73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="27" t="inlineStr">
+      <c r="A74" s="36" t="inlineStr">
         <is>
           <t>SALSA BOLOGNESA (u)</t>
         </is>
       </c>
-      <c r="B74" s="27" t="inlineStr"/>
-      <c r="C74" s="27" t="inlineStr"/>
-      <c r="D74" s="27" t="inlineStr"/>
-      <c r="E74" s="27" t="inlineStr"/>
-      <c r="F74" s="28" t="n">
+      <c r="B74" s="36" t="inlineStr"/>
+      <c r="C74" s="36" t="inlineStr"/>
+      <c r="D74" s="36" t="inlineStr"/>
+      <c r="E74" s="36" t="inlineStr"/>
+      <c r="F74" s="37" t="n">
         <v>6850</v>
       </c>
-      <c r="G74" s="27" t="inlineStr"/>
-      <c r="H74" s="27" t="inlineStr">
+      <c r="G74" s="36" t="inlineStr"/>
+      <c r="H74" s="36" t="inlineStr">
         <is>
           <t>2.2%</t>
         </is>
@@ -6074,7 +6009,7 @@
           <t xml:space="preserve">  Carne picada</t>
         </is>
       </c>
-      <c r="B75" s="12" t="n">
+      <c r="B75" s="13" t="n">
         <v>0.3</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
@@ -6082,10 +6017,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D75" s="12" t="n">
+      <c r="D75" s="13" t="n">
         <v>3660</v>
       </c>
-      <c r="E75" s="12" t="n">
+      <c r="E75" s="13" t="n">
         <v>2562</v>
       </c>
       <c r="F75" s="9" t="inlineStr"/>
@@ -6098,7 +6033,7 @@
           <t xml:space="preserve">  Tomate triturado</t>
         </is>
       </c>
-      <c r="B76" s="12" t="n">
+      <c r="B76" s="13" t="n">
         <v>0.5</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -6106,10 +6041,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D76" s="12" t="n">
+      <c r="D76" s="13" t="n">
         <v>755</v>
       </c>
-      <c r="E76" s="12" t="n">
+      <c r="E76" s="13" t="n">
         <v>528</v>
       </c>
       <c r="F76" s="9" t="inlineStr"/>
@@ -6122,7 +6057,7 @@
           <t xml:space="preserve">  Cebolla/condimentos</t>
         </is>
       </c>
-      <c r="B77" s="29" t="n">
+      <c r="B77" s="38" t="n">
         <v>1</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
@@ -6130,10 +6065,10 @@
           <t>lote</t>
         </is>
       </c>
-      <c r="D77" s="12" t="n">
+      <c r="D77" s="13" t="n">
         <v>400</v>
       </c>
-      <c r="E77" s="12" t="n">
+      <c r="E77" s="13" t="n">
         <v>280</v>
       </c>
       <c r="F77" s="9" t="inlineStr"/>
@@ -6181,34 +6116,34 @@
       <c r="H80" s="7" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="18" t="inlineStr">
+      <c r="A81" s="24" t="inlineStr">
         <is>
           <t>Margen asumido en estructura de costos</t>
         </is>
       </c>
-      <c r="B81" s="18" t="inlineStr"/>
-      <c r="C81" s="18" t="inlineStr"/>
-      <c r="D81" s="18" t="inlineStr"/>
-      <c r="E81" s="18" t="inlineStr"/>
-      <c r="F81" s="18" t="inlineStr"/>
-      <c r="G81" s="18" t="inlineStr">
+      <c r="B81" s="24" t="inlineStr"/>
+      <c r="C81" s="24" t="inlineStr"/>
+      <c r="D81" s="24" t="inlineStr"/>
+      <c r="E81" s="24" t="inlineStr"/>
+      <c r="F81" s="24" t="inlineStr"/>
+      <c r="G81" s="24" t="inlineStr">
         <is>
           <t>30.0%</t>
         </is>
       </c>
-      <c r="H81" s="18" t="inlineStr"/>
+      <c r="H81" s="24" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Factor costo 0.70 = precio retail del super × 70% (margen tipico supermercado ~30%). Ajustar si se conoce el costo real.</t>
+          <t xml:space="preserve">  Factor costo 0.70 = precio retail x 70% (margen tipico supermercado ~30%)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Verde = margen &gt;25% | Amarillo = margen 0-25% | Rojo = margen negativo (vende a perdida)</t>
+          <t xml:space="preserve">  Verde = margen &gt;25% | Amarillo = margen 0-25% | Rojo = margen negativo</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6185,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Escenarios variando Margen Bruto y Merma:</t>
         </is>
@@ -6289,157 +6224,157 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>Pesimista</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="40" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="D6" s="32" t="n">
-        <v>-4219444</v>
-      </c>
-      <c r="E6" s="31" t="inlineStr">
-        <is>
-          <t>-38.2%</t>
-        </is>
-      </c>
-      <c r="F6" s="31" t="inlineStr">
+      <c r="D6" s="41" t="n">
+        <v>-3985013</v>
+      </c>
+      <c r="E6" s="40" t="inlineStr">
+        <is>
+          <t>-36.1%</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
         <is>
           <t>DEFICIT</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Conservador</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D7" s="32" t="n">
-        <v>-3666926</v>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t>-33.2%</t>
-        </is>
-      </c>
-      <c r="F7" s="31" t="inlineStr">
+      <c r="D7" s="41" t="n">
+        <v>-3432495</v>
+      </c>
+      <c r="E7" s="40" t="inlineStr">
+        <is>
+          <t>-31.1%</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
         <is>
           <t>DEFICIT</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D8" s="32" t="n">
-        <v>-3335415</v>
-      </c>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>-30.2%</t>
-        </is>
-      </c>
-      <c r="F8" s="31" t="inlineStr">
+      <c r="D8" s="41" t="n">
+        <v>-3100984</v>
+      </c>
+      <c r="E8" s="40" t="inlineStr">
+        <is>
+          <t>-28.1%</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
         <is>
           <t>DEFICIT</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>Optimista</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C9" s="40" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D9" s="32" t="n">
-        <v>-2782898</v>
-      </c>
-      <c r="E9" s="31" t="inlineStr">
-        <is>
-          <t>-25.2%</t>
-        </is>
-      </c>
-      <c r="F9" s="31" t="inlineStr">
+      <c r="D9" s="41" t="n">
+        <v>-2548467</v>
+      </c>
+      <c r="E9" s="40" t="inlineStr">
+        <is>
+          <t>-23.1%</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
         <is>
           <t>DEFICIT</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>Ideal</t>
         </is>
       </c>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="40" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D10" s="32" t="n">
-        <v>-2451388</v>
-      </c>
-      <c r="E10" s="31" t="inlineStr">
-        <is>
-          <t>-22.2%</t>
-        </is>
-      </c>
-      <c r="F10" s="31" t="inlineStr">
+      <c r="D10" s="41" t="n">
+        <v>-2216957</v>
+      </c>
+      <c r="E10" s="40" t="inlineStr">
+        <is>
+          <t>-20.1%</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
         <is>
           <t>DEFICIT</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>Punto de equilibrio por escenario:</t>
         </is>
@@ -6478,150 +6413,150 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>Pesimista</t>
         </is>
       </c>
-      <c r="B15" s="31" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C15" s="40" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="D15" s="32" t="n">
-        <v>45501168</v>
-      </c>
-      <c r="E15" s="31" t="inlineStr">
-        <is>
-          <t>24%</t>
-        </is>
-      </c>
-      <c r="F15" s="31" t="inlineStr">
+      <c r="D15" s="41" t="n">
+        <v>43721525</v>
+      </c>
+      <c r="E15" s="40" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
         <is>
           <t>INSUFICIENTE</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>Conservador</t>
         </is>
       </c>
-      <c r="B16" s="31" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="C16" s="31" t="inlineStr">
+      <c r="C16" s="40" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D16" s="32" t="n">
-        <v>32310686</v>
-      </c>
-      <c r="E16" s="31" t="inlineStr">
-        <is>
-          <t>34%</t>
-        </is>
-      </c>
-      <c r="F16" s="31" t="inlineStr">
+      <c r="D16" s="41" t="n">
+        <v>31009807</v>
+      </c>
+      <c r="E16" s="40" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
         <is>
           <t>INSUFICIENTE</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="B17" s="31" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="C17" s="31" t="inlineStr">
+      <c r="C17" s="40" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D17" s="32" t="n">
-        <v>27523375</v>
-      </c>
-      <c r="E17" s="31" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="F17" s="31" t="inlineStr">
+      <c r="D17" s="41" t="n">
+        <v>26403776</v>
+      </c>
+      <c r="E17" s="40" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
         <is>
           <t>INSUFICIENTE</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>Optimista</t>
         </is>
       </c>
-      <c r="B18" s="31" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="C18" s="31" t="inlineStr">
+      <c r="C18" s="40" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D18" s="32" t="n">
-        <v>22072712</v>
-      </c>
-      <c r="E18" s="31" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="F18" s="31" t="inlineStr">
+      <c r="D18" s="41" t="n">
+        <v>21164377</v>
+      </c>
+      <c r="E18" s="40" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
         <is>
           <t>INSUFICIENTE</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>Ideal</t>
         </is>
       </c>
-      <c r="B19" s="31" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="C19" s="31" t="inlineStr">
+      <c r="C19" s="40" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D19" s="32" t="n">
-        <v>19728522</v>
-      </c>
-      <c r="E19" s="31" t="inlineStr">
-        <is>
-          <t>56%</t>
-        </is>
-      </c>
-      <c r="F19" s="31" t="inlineStr">
+      <c r="D19" s="41" t="n">
+        <v>18912638</v>
+      </c>
+      <c r="E19" s="40" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
         <is>
           <t>INSUFICIENTE</t>
         </is>
@@ -6630,7 +6565,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NOTA: Si la empresa obtiene certificado MiPyME, las contribuciones bajan de 20.4% a 18% SUSS, mejorando todos los escenarios.</t>
+          <t xml:space="preserve">  NOTA: Si obtiene certificado MiPyME, contribuciones SUSS bajan de 20.74% a ~18%, mejorando todos los escenarios.</t>
         </is>
       </c>
     </row>

--- a/nino/ROTICERIA/Estructura_Costos_Rotiseria_NINO.xlsx
+++ b/nino/ROTICERIA/Estructura_Costos_Rotiseria_NINO.xlsx
@@ -624,7 +624,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Base: ultimos 31 dias (16/02/2026 - 18/03/2026) desestacionalizado | Elaborado: Marzo 2026</t>
+          <t>Base: ultimos 31 dias (01/03/2026 - 31/03/2026) desestacionalizado | Elaborado: Marzo 2026</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>11050346</v>
+        <v>10139550</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tickets promedio/mes: 1,139 | Ticket prom: $9,702</t>
+          <t xml:space="preserve">  Tickets promedio/mes: 1,119 | Ticket prom: $9,061</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr"/>
@@ -741,7 +741,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Efectivo 40.8% | Debito 26.7% | Credito 19.0% | Billetera 13.4%</t>
+          <t xml:space="preserve">  Efectivo 38.9% | Debito 25.5% | Credito 18.1% | Billetera 12.8%</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr"/>
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>-3855659</v>
+        <v>-3570698</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -840,11 +840,11 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>-1709147</v>
+        <v>-1556444</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>-660855</v>
+        <v>-600677</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -890,16 +890,16 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>-431885</v>
+        <v>-387991</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>-163088</v>
+        <v>-149541</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -940,11 +940,11 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>-914608</v>
+        <v>-832334</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -1623,11 +1623,11 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Tarjeta Credito (19.0% ventas)</t>
+          <t>Tarjeta Credito (18.1% ventas)</t>
         </is>
       </c>
       <c r="B63" s="6">
-        <f>-B8*0.190142*0.03</f>
+        <f>-B8*0.181058*0.03</f>
         <v/>
       </c>
       <c r="C63" s="23">
@@ -1648,11 +1648,11 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Tarjeta Debito (26.7% ventas)</t>
+          <t>Tarjeta Debito (25.5% ventas)</t>
         </is>
       </c>
       <c r="B64" s="6">
-        <f>-B8*0.267352*0.012</f>
+        <f>-B8*0.254579*0.012</f>
         <v/>
       </c>
       <c r="C64" s="23">
@@ -1673,11 +1673,11 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Billetera Virtual (13.4% ventas)</t>
+          <t>Billetera Virtual (12.8% ventas)</t>
         </is>
       </c>
       <c r="B65" s="6">
-        <f>-B8*0.134232*0.015</f>
+        <f>-B8*0.127820*0.015</f>
         <v/>
       </c>
       <c r="C65" s="23">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="B70" s="6">
-        <f>-B8*0.591727*0.012</f>
+        <f>-B8*0.611232*0.012</f>
         <v/>
       </c>
       <c r="C70" s="23">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Ley 25.413. Solo s/bancarizado (59.2% ventas, excluye efectivo)</t>
+          <t>Ley 25.413. Solo s/bancarizado (61.1% ventas, excluye efectivo)</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9. Imp. Debitos/Creditos: 1.2% SOLO sobre bancarizado (59.2% ventas). Ley 25.413</t>
+          <t xml:space="preserve">  9. Imp. Debitos/Creditos: 1.2% SOLO sobre bancarizado (61.1% ventas). Ley 25.413</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  12. Ventas: ultimos 31 dias reales (16/02/2026 - 18/03/2026) desestacionalizados con indice 2025</t>
+          <t xml:space="preserve">  12. Ventas: ultimos 31 dias reales (01/03/2026 - 31/03/2026) desestacionalizados con indice 2025</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2793,16 +2793,16 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>6745218</v>
+        <v>11630829</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>666</v>
+        <v>1189</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>750</v>
+        <v>1308</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>10128</v>
+        <v>9782</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>3319368</v>
@@ -2817,26 +2817,57 @@
         <v>1542596</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>2946040</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>278</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>376</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>10597</v>
+      </c>
+      <c r="F22" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n">
-        <v>156097009</v>
-      </c>
-      <c r="C23" s="8" t="n">
-        <v>19257</v>
-      </c>
-      <c r="D23" s="8" t="n">
-        <v>20270</v>
-      </c>
-      <c r="E23" s="7" t="inlineStr"/>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr"/>
+      <c r="B24" s="8" t="n">
+        <v>163928660</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>20058</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>21205</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr"/>
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2852,7 +2883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2909,19 +2940,19 @@
         </is>
       </c>
       <c r="B4" s="33" t="n">
-        <v>21848114</v>
+        <v>22833889</v>
       </c>
       <c r="C4" s="33" t="n">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="D4" s="33" t="n">
-        <v>35085</v>
+        <v>35563</v>
       </c>
       <c r="E4" s="33" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="5">
@@ -2931,13 +2962,13 @@
         </is>
       </c>
       <c r="B5" s="33" t="n">
-        <v>21267910</v>
+        <v>22334910</v>
       </c>
       <c r="C5" s="33" t="n">
-        <v>2520</v>
+        <v>2617</v>
       </c>
       <c r="D5" s="33" t="n">
-        <v>8343</v>
+        <v>8421</v>
       </c>
       <c r="E5" s="33" t="n">
         <v>13.6</v>
@@ -2953,19 +2984,19 @@
         </is>
       </c>
       <c r="B6" s="33" t="n">
-        <v>18840000</v>
+        <v>19632000</v>
       </c>
       <c r="C6" s="33" t="n">
-        <v>4367</v>
+        <v>4511</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>4292</v>
+        <v>4329</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>39.7</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="7">
@@ -2975,19 +3006,19 @@
         </is>
       </c>
       <c r="B7" s="33" t="n">
-        <v>8315100</v>
+        <v>8766100</v>
       </c>
       <c r="C7" s="33" t="n">
-        <v>1937</v>
+        <v>2019</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>4270</v>
+        <v>4319</v>
       </c>
       <c r="E7" s="33" t="n">
         <v>5.3</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="8">
@@ -2997,19 +3028,19 @@
         </is>
       </c>
       <c r="B8" s="33" t="n">
-        <v>7180250</v>
+        <v>7532250</v>
       </c>
       <c r="C8" s="33" t="n">
-        <v>1657</v>
+        <v>1721</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>4321</v>
+        <v>4360</v>
       </c>
       <c r="E8" s="33" t="n">
         <v>4.6</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="9">
@@ -3019,63 +3050,63 @@
         </is>
       </c>
       <c r="B9" s="33" t="n">
-        <v>4547066</v>
+        <v>4769941</v>
       </c>
       <c r="C9" s="34" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>16005</v>
+        <v>16289</v>
       </c>
       <c r="E9" s="33" t="n">
         <v>2.9</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="32" t="inlineStr">
         <is>
-          <t>MIGA TRIP. X 12 UNI.</t>
+          <t>EMPANADA VERDURA X 6 UN.</t>
         </is>
       </c>
       <c r="B10" s="33" t="n">
-        <v>4231800</v>
+        <v>4410850</v>
       </c>
       <c r="C10" s="33" t="n">
-        <v>494</v>
+        <v>1017</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>8528</v>
+        <v>4320</v>
       </c>
       <c r="E10" s="33" t="n">
         <v>2.7</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>55.2</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="32" t="inlineStr">
         <is>
-          <t>EMPANADA VERDURA X 6 UN.</t>
+          <t>MIGA TRIP. X 12 UNI.</t>
         </is>
       </c>
       <c r="B11" s="33" t="n">
-        <v>4124850</v>
+        <v>4378050</v>
       </c>
       <c r="C11" s="33" t="n">
-        <v>965</v>
+        <v>509</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>4257</v>
+        <v>8564</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>57.9</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="12">
@@ -3085,19 +3116,19 @@
         </is>
       </c>
       <c r="B12" s="33" t="n">
-        <v>3978000</v>
+        <v>4231000</v>
       </c>
       <c r="C12" s="33" t="n">
-        <v>936</v>
+        <v>982</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>4241</v>
+        <v>4301</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>60.4</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="13">
@@ -3107,63 +3138,63 @@
         </is>
       </c>
       <c r="B13" s="33" t="n">
-        <v>3952006</v>
+        <v>4075171</v>
       </c>
       <c r="C13" s="34" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>22047</v>
+        <v>22293</v>
       </c>
       <c r="E13" s="33" t="n">
         <v>2.5</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>63</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="32" t="inlineStr">
         <is>
-          <t>PIZZA C/JAMON NINO</t>
+          <t>EMPANADA CAPRESE X 6 UN.</t>
         </is>
       </c>
       <c r="B14" s="33" t="n">
-        <v>3599100</v>
+        <v>3821000</v>
       </c>
       <c r="C14" s="33" t="n">
-        <v>446</v>
+        <v>877</v>
       </c>
       <c r="D14" s="33" t="n">
-        <v>7997</v>
+        <v>4323</v>
       </c>
       <c r="E14" s="33" t="n">
         <v>2.3</v>
       </c>
       <c r="F14" s="33" t="n">
-        <v>65.3</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="32" t="inlineStr">
         <is>
-          <t>EMPANADA CAPRESE X 6 UN.</t>
+          <t>PIZZA C/JAMON NINO</t>
         </is>
       </c>
       <c r="B15" s="33" t="n">
-        <v>3584500</v>
+        <v>3757500</v>
       </c>
       <c r="C15" s="33" t="n">
-        <v>834</v>
+        <v>462</v>
       </c>
       <c r="D15" s="33" t="n">
-        <v>4262</v>
+        <v>8062</v>
       </c>
       <c r="E15" s="33" t="n">
         <v>2.3</v>
       </c>
       <c r="F15" s="33" t="n">
-        <v>67.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -3173,19 +3204,19 @@
         </is>
       </c>
       <c r="B16" s="33" t="n">
-        <v>3516596</v>
+        <v>3629901</v>
       </c>
       <c r="C16" s="34" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D16" s="33" t="n">
-        <v>23536</v>
+        <v>23787</v>
       </c>
       <c r="E16" s="33" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F16" s="33" t="n">
-        <v>69.8</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3195,19 +3226,19 @@
         </is>
       </c>
       <c r="B17" s="33" t="n">
-        <v>3500210</v>
+        <v>3625899</v>
       </c>
       <c r="C17" s="33" t="n">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D17" s="33" t="n">
-        <v>10984</v>
+        <v>11106</v>
       </c>
       <c r="E17" s="33" t="n">
         <v>2.2</v>
       </c>
       <c r="F17" s="33" t="n">
-        <v>72.09999999999999</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -3217,19 +3248,19 @@
         </is>
       </c>
       <c r="B18" s="33" t="n">
-        <v>3428000</v>
+        <v>3570500</v>
       </c>
       <c r="C18" s="33" t="n">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="D18" s="33" t="n">
-        <v>6308</v>
+        <v>6349</v>
       </c>
       <c r="E18" s="33" t="n">
         <v>2.2</v>
       </c>
       <c r="F18" s="33" t="n">
-        <v>74.3</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
@@ -3239,63 +3270,63 @@
         </is>
       </c>
       <c r="B19" s="33" t="n">
-        <v>3291113</v>
+        <v>3453800</v>
       </c>
       <c r="C19" s="33" t="n">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="D19" s="33" t="n">
-        <v>7335</v>
+        <v>7415</v>
       </c>
       <c r="E19" s="33" t="n">
         <v>2.1</v>
       </c>
       <c r="F19" s="33" t="n">
-        <v>76.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="32" t="inlineStr">
         <is>
-          <t>MIGA TRIP. X 6 UNI.</t>
+          <t>EMPANADA J&amp;Q X 12 UN.</t>
         </is>
       </c>
       <c r="B20" s="33" t="n">
-        <v>3003880</v>
+        <v>3128400</v>
       </c>
       <c r="C20" s="33" t="n">
-        <v>680</v>
+        <v>366</v>
       </c>
       <c r="D20" s="33" t="n">
-        <v>4366</v>
+        <v>8573</v>
       </c>
       <c r="E20" s="33" t="n">
         <v>1.9</v>
       </c>
       <c r="F20" s="33" t="n">
-        <v>78.3</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>EMPANADA J&amp;Q X 12 UN.</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="n">
-        <v>2985400</v>
-      </c>
-      <c r="C21" s="21" t="n">
-        <v>353</v>
-      </c>
-      <c r="D21" s="21" t="n">
-        <v>8475</v>
-      </c>
-      <c r="E21" s="21" t="n">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>MIGA TRIP. X 6 UNI.</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="n">
+        <v>3103280</v>
+      </c>
+      <c r="C21" s="33" t="n">
+        <v>700</v>
+      </c>
+      <c r="D21" s="33" t="n">
+        <v>4383</v>
+      </c>
+      <c r="E21" s="33" t="n">
         <v>1.9</v>
       </c>
-      <c r="F21" s="21" t="n">
-        <v>80.2</v>
+      <c r="F21" s="33" t="n">
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3305,19 +3336,19 @@
         </is>
       </c>
       <c r="B22" s="21" t="n">
-        <v>2909900</v>
+        <v>3047400</v>
       </c>
       <c r="C22" s="21" t="n">
-        <v>670</v>
+        <v>695</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>4317</v>
+        <v>4360</v>
       </c>
       <c r="E22" s="21" t="n">
         <v>1.9</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>82.09999999999999</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="23">
@@ -3327,19 +3358,19 @@
         </is>
       </c>
       <c r="B23" s="21" t="n">
-        <v>2737178</v>
-      </c>
-      <c r="C23" s="35" t="n">
-        <v>83</v>
+        <v>2880190</v>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>101</v>
       </c>
       <c r="D23" s="21" t="n">
-        <v>7284</v>
+        <v>7306</v>
       </c>
       <c r="E23" s="21" t="n">
         <v>1.8</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -3349,19 +3380,19 @@
         </is>
       </c>
       <c r="B24" s="21" t="n">
-        <v>2646077</v>
+        <v>2781713</v>
       </c>
       <c r="C24" s="35" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>7533</v>
+        <v>7584</v>
       </c>
       <c r="E24" s="21" t="n">
         <v>1.7</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>85.5</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="25">
@@ -3371,19 +3402,19 @@
         </is>
       </c>
       <c r="B25" s="21" t="n">
-        <v>2565688</v>
+        <v>2664458</v>
       </c>
       <c r="C25" s="21" t="n">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D25" s="21" t="n">
-        <v>4397</v>
+        <v>4407</v>
       </c>
       <c r="E25" s="21" t="n">
         <v>1.6</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>87.2</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -3393,19 +3424,19 @@
         </is>
       </c>
       <c r="B26" s="21" t="n">
-        <v>2369794</v>
+        <v>2484229</v>
       </c>
       <c r="C26" s="21" t="n">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>4224</v>
+        <v>4236</v>
       </c>
       <c r="E26" s="21" t="n">
         <v>1.5</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>88.7</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3415,85 +3446,85 @@
         </is>
       </c>
       <c r="B27" s="21" t="n">
-        <v>2348123</v>
+        <v>2468583</v>
       </c>
       <c r="C27" s="21" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D27" s="21" t="n">
-        <v>20965</v>
+        <v>21281</v>
       </c>
       <c r="E27" s="21" t="n">
         <v>1.5</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>90.2</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>ARROZ CON POLLO</t>
+          <t>EMPANADA ATUN X 6 UN.</t>
         </is>
       </c>
       <c r="B28" s="21" t="n">
-        <v>1409643</v>
+        <v>1577350</v>
       </c>
       <c r="C28" s="21" t="n">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="D28" s="21" t="n">
-        <v>7172</v>
+        <v>4992</v>
       </c>
       <c r="E28" s="21" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>91.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>CANELONES VERD Y RIC NINO</t>
+          <t>ARROZ CON POLLO</t>
         </is>
       </c>
       <c r="B29" s="21" t="n">
-        <v>1396833</v>
+        <v>1464114</v>
       </c>
       <c r="C29" s="21" t="n">
-        <v>169</v>
+        <v>291</v>
       </c>
       <c r="D29" s="21" t="n">
-        <v>10788</v>
+        <v>7197</v>
       </c>
       <c r="E29" s="21" t="n">
         <v>0.9</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>92</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>EMPANADA ATUN X 6 UN.</t>
+          <t>CANELONES VERD Y RIC NINO</t>
         </is>
       </c>
       <c r="B30" s="21" t="n">
-        <v>1375350</v>
+        <v>1461149</v>
       </c>
       <c r="C30" s="21" t="n">
-        <v>282</v>
+        <v>174</v>
       </c>
       <c r="D30" s="21" t="n">
-        <v>4877</v>
+        <v>10947</v>
       </c>
       <c r="E30" s="21" t="n">
         <v>0.9</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>92.90000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="31">
@@ -3503,107 +3534,107 @@
         </is>
       </c>
       <c r="B31" s="21" t="n">
-        <v>1345642</v>
+        <v>1408387</v>
       </c>
       <c r="C31" s="35" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D31" s="21" t="n">
-        <v>8168</v>
+        <v>8160</v>
       </c>
       <c r="E31" s="21" t="n">
         <v>0.9</v>
       </c>
       <c r="F31" s="21" t="n">
-        <v>93.7</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>MIGA TRIPLE X 100 UN.</t>
+          <t>POROTOS ALIÑADOS NINO</t>
         </is>
       </c>
       <c r="B32" s="21" t="n">
-        <v>1296900</v>
+        <v>1320310</v>
       </c>
       <c r="C32" s="35" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>44907</v>
+        <v>8773</v>
       </c>
       <c r="E32" s="21" t="n">
         <v>0.8</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>94.59999999999999</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>POROTOS ALIÑADOS NINO</t>
+          <t>EMPANADA CARNE X 18 UN.</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>1292645</v>
+        <v>1304700</v>
       </c>
       <c r="C33" s="31" t="n">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>8735</v>
+        <v>12918</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>0.8</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>95.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>CANELONES HUMITA NINO</t>
+          <t>MIGA TRIPLE X 100 UN.</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>1241353</v>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>145</v>
+        <v>1296900</v>
+      </c>
+      <c r="C34" s="31" t="n">
+        <v>22</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>11069</v>
+        <v>44907</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>0.8</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>96.2</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>EMPANADA CARNE X 18 UN.</t>
+          <t>CANELONES HUMITA NINO</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>1189200</v>
-      </c>
-      <c r="C35" s="31" t="n">
-        <v>92</v>
+        <v>1287701</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>148</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>12651</v>
+        <v>11194</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>0.8</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>96.90000000000001</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="36">
@@ -3625,7 +3656,7 @@
         <v>0.5</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>97.5</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="37">
@@ -3635,19 +3666,19 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>626764</v>
+        <v>638842</v>
       </c>
       <c r="C37" s="31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>5323</v>
+        <v>5335</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>0.4</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>97.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -3669,7 +3700,7 @@
         <v>0.4</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>98.3</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39">
@@ -3691,7 +3722,7 @@
         <v>0.3</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>98.59999999999999</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="40">
@@ -3701,41 +3732,41 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>289900</v>
+        <v>443900</v>
       </c>
       <c r="C40" s="31" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>8267</v>
+        <v>9048</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>98.7</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>CEBOLLITAS EN ESCABECHE NINO</t>
+          <t>EMPANADA ATUN X 12 UN.</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>188480</v>
+        <v>328800</v>
       </c>
       <c r="C41" s="31" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>4317</v>
+        <v>11262</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>98.90000000000001</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="42">
@@ -3745,41 +3776,41 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>180350</v>
+        <v>196850</v>
       </c>
       <c r="C42" s="31" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>3972</v>
+        <v>4076</v>
       </c>
       <c r="E42" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>99</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>PIZZA FUGAZZA NINO</t>
+          <t>CEBOLLITAS EN ESCABECHE NINO</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>170540</v>
+        <v>188480</v>
       </c>
       <c r="C43" s="31" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>4632</v>
+        <v>4317</v>
       </c>
       <c r="E43" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>99.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -3789,57 +3820,57 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>159150</v>
+        <v>175650</v>
       </c>
       <c r="C44" s="31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>13262</v>
+        <v>13512</v>
       </c>
       <c r="E44" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>99.2</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>EMPANADA CAPRESE X12 UN.</t>
+          <t>EMPANADA VERDURA X 12 UN.</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>128100</v>
+        <v>171500</v>
       </c>
       <c r="C45" s="31" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>9200</v>
+        <v>9344</v>
       </c>
       <c r="E45" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>EMPANADA POR UNIDAD</t>
+          <t>PIZZA FUGAZZA NINO</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>126850</v>
-      </c>
-      <c r="C46" s="6" t="n">
-        <v>158</v>
+        <v>170540</v>
+      </c>
+      <c r="C46" s="31" t="n">
+        <v>37</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>806</v>
+        <v>4632</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>0.1</v>
@@ -3851,17 +3882,17 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>MIGA SIMP. J Y Q X 100 U</t>
+          <t>EMPANADA CAPRESE X12 UN.</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>122000</v>
+        <v>161100</v>
       </c>
       <c r="C47" s="31" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>15250</v>
+        <v>9586</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>0.1</v>
@@ -3873,39 +3904,39 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>EMPANADA CARNE X 3 UN.</t>
+          <t>EMPANADA POR UNIDAD</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>100700</v>
-      </c>
-      <c r="C48" s="31" t="n">
-        <v>45</v>
+        <v>138850</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>170</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>2238</v>
+        <v>814</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>EMPANADA POLLO X 3 UN.</t>
+          <t>MIGA SIMP. J Y Q X 100 U</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>83500</v>
+        <v>122000</v>
       </c>
       <c r="C49" s="31" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>2197</v>
+        <v>15250</v>
       </c>
       <c r="E49" s="6" t="n">
         <v>0.1</v>
@@ -3917,17 +3948,17 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>EMPANADA VERDURA X 12 UN.</t>
+          <t>EMPANADA CARNE X 3 UN.</t>
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>83500</v>
+        <v>108950</v>
       </c>
       <c r="C50" s="31" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>8350</v>
+        <v>2270</v>
       </c>
       <c r="E50" s="6" t="n">
         <v>0.1</v>
@@ -3939,17 +3970,17 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>EMPANADA CAPRESE X 3 UN.</t>
+          <t>EMPANADA POLLO X 3 UN.</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>79300</v>
+        <v>89000</v>
       </c>
       <c r="C51" s="31" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>2083</v>
+        <v>2225</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>0.1</v>
@@ -3961,17 +3992,17 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>ALIÑO CHIMICHURRI NINO</t>
+          <t>EMPANADA CAPRESE X 3 UN.</t>
         </is>
       </c>
       <c r="B52" s="6" t="n">
-        <v>77342</v>
+        <v>79300</v>
       </c>
       <c r="C52" s="31" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>12736</v>
+        <v>2083</v>
       </c>
       <c r="E52" s="6" t="n">
         <v>0</v>
@@ -3983,17 +4014,17 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>EMPANADA ATUN X 12 UN.</t>
+          <t>ALIÑO CHIMICHURRI NINO</t>
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>76800</v>
+        <v>77342</v>
       </c>
       <c r="C53" s="31" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>9600</v>
+        <v>12736</v>
       </c>
       <c r="E53" s="6" t="n">
         <v>0</v>
@@ -4005,17 +4036,17 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>EMPANADA J&amp;Q X 3 UN.</t>
+          <t>EMPANADA CEB/QUEX12 UN.</t>
         </is>
       </c>
       <c r="B54" s="6" t="n">
-        <v>59650</v>
+        <v>63200</v>
       </c>
       <c r="C54" s="31" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>2218</v>
+        <v>8883</v>
       </c>
       <c r="E54" s="6" t="n">
         <v>0</v>
@@ -4027,17 +4058,17 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>EMPANADA CEB/QUEX12 UN.</t>
+          <t>EMPANADA J&amp;Q X 3 UN.</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>52200</v>
+        <v>62400</v>
       </c>
       <c r="C55" s="31" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>8460</v>
+        <v>2245</v>
       </c>
       <c r="E55" s="6" t="n">
         <v>0</v>
@@ -4065,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="57">
@@ -4075,13 +4106,13 @@
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>45100</v>
+        <v>51100</v>
       </c>
       <c r="C57" s="31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>2374</v>
+        <v>2433</v>
       </c>
       <c r="E57" s="6" t="n">
         <v>0</v>
@@ -4097,13 +4128,13 @@
         </is>
       </c>
       <c r="B58" s="6" t="n">
-        <v>40600</v>
+        <v>45180</v>
       </c>
       <c r="C58" s="31" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>1467</v>
+        <v>1530</v>
       </c>
       <c r="E58" s="6" t="n">
         <v>0</v>
@@ -4119,13 +4150,13 @@
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>37550</v>
+        <v>43050</v>
       </c>
       <c r="C59" s="31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>2209</v>
+        <v>2266</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>0</v>
@@ -4153,23 +4184,23 @@
         <v>0</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>MIGA SAL /QUE X 12 UN.</t>
+          <t>EMPANADA VERDURA X 3 UN.</t>
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>21000</v>
+        <v>24700</v>
       </c>
       <c r="C61" s="31" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>10500</v>
+        <v>2245</v>
       </c>
       <c r="E61" s="6" t="n">
         <v>0</v>
@@ -4181,17 +4212,17 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>EMPANADA VERDURA X 3 UN.</t>
+          <t>MIGA SAL /QUE X 12 UN.</t>
         </is>
       </c>
       <c r="B62" s="6" t="n">
-        <v>19200</v>
+        <v>21000</v>
       </c>
       <c r="C62" s="31" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>2133</v>
+        <v>10500</v>
       </c>
       <c r="E62" s="6" t="n">
         <v>0</v>
@@ -4203,17 +4234,17 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>EMPANADA POLLO X 1 UN.</t>
+          <t>EMPANADA ATUN 1 UN.</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>14900</v>
+        <v>16500</v>
       </c>
       <c r="C63" s="31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>745</v>
+        <v>893</v>
       </c>
       <c r="E63" s="6" t="n">
         <v>0</v>
@@ -4225,17 +4256,17 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>EMPANADA ATUN 1 UN.</t>
+          <t>EMPANADA POLLO X 1 UN.</t>
         </is>
       </c>
       <c r="B64" s="6" t="n">
-        <v>6500</v>
+        <v>14900</v>
       </c>
       <c r="C64" s="31" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>812</v>
+        <v>745</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>0</v>
@@ -4269,17 +4300,17 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>MIGA SAL / QUE X 6 UN.</t>
+          <t>ENSALADA POLLO C/CHOCLO</t>
         </is>
       </c>
       <c r="B66" s="6" t="n">
-        <v>4050</v>
+        <v>5088</v>
       </c>
       <c r="C66" s="31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>4050</v>
+        <v>18500</v>
       </c>
       <c r="E66" s="6" t="n">
         <v>0</v>
@@ -4291,17 +4322,17 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>VITEL TONE NINO</t>
+          <t>MIGA SAL / QUE X 6 UN.</t>
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>218</v>
+        <v>4050</v>
       </c>
       <c r="C67" s="31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>1900</v>
+        <v>4050</v>
       </c>
       <c r="E67" s="6" t="n">
         <v>0</v>
@@ -4310,8 +4341,30 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>VITEL TONE NINO</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>218</v>
+      </c>
+      <c r="C68" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>1900</v>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Verde = Core (80%) | Amarillo = Complementario (80-95%) | Sin color = Marginal</t>
         </is>
@@ -4319,8 +4372,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A69:F69"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A70:F70"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6240,11 +6293,11 @@
         </is>
       </c>
       <c r="D6" s="41" t="n">
-        <v>-3985013</v>
+        <v>-4093185</v>
       </c>
       <c r="E6" s="40" t="inlineStr">
         <is>
-          <t>-36.1%</t>
+          <t>-40.4%</t>
         </is>
       </c>
       <c r="F6" s="40" t="inlineStr">
@@ -6270,11 +6323,11 @@
         </is>
       </c>
       <c r="D7" s="41" t="n">
-        <v>-3432495</v>
+        <v>-3586208</v>
       </c>
       <c r="E7" s="40" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-35.4%</t>
         </is>
       </c>
       <c r="F7" s="40" t="inlineStr">
@@ -6300,11 +6353,11 @@
         </is>
       </c>
       <c r="D8" s="41" t="n">
-        <v>-3100984</v>
+        <v>-3282022</v>
       </c>
       <c r="E8" s="40" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="F8" s="40" t="inlineStr">
@@ -6330,11 +6383,11 @@
         </is>
       </c>
       <c r="D9" s="41" t="n">
-        <v>-2548467</v>
+        <v>-2775043</v>
       </c>
       <c r="E9" s="40" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="F9" s="40" t="inlineStr">
@@ -6360,11 +6413,11 @@
         </is>
       </c>
       <c r="D10" s="41" t="n">
-        <v>-2216957</v>
+        <v>-2470858</v>
       </c>
       <c r="E10" s="40" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="F10" s="40" t="inlineStr">
@@ -6429,11 +6482,11 @@
         </is>
       </c>
       <c r="D15" s="41" t="n">
-        <v>43721525</v>
+        <v>43618547</v>
       </c>
       <c r="E15" s="40" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="F15" s="40" t="inlineStr">
@@ -6459,11 +6512,11 @@
         </is>
       </c>
       <c r="D16" s="41" t="n">
-        <v>31009807</v>
+        <v>30957970</v>
       </c>
       <c r="E16" s="40" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="F16" s="40" t="inlineStr">
@@ -6489,11 +6542,11 @@
         </is>
       </c>
       <c r="D17" s="41" t="n">
-        <v>26403776</v>
+        <v>26366198</v>
       </c>
       <c r="E17" s="40" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="F17" s="40" t="inlineStr">
@@ -6519,11 +6572,11 @@
         </is>
       </c>
       <c r="D18" s="41" t="n">
-        <v>21164377</v>
+        <v>21140219</v>
       </c>
       <c r="E18" s="40" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="F18" s="40" t="inlineStr">
@@ -6549,11 +6602,11 @@
         </is>
       </c>
       <c r="D19" s="41" t="n">
-        <v>18912638</v>
+        <v>18893345</v>
       </c>
       <c r="E19" s="40" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="F19" s="40" t="inlineStr">
